--- a/jogos_2025-04-24.xlsx
+++ b/jogos_2025-04-24.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="197">
   <si>
     <t>Date</t>
   </si>
@@ -127,60 +127,6 @@
     <t>awayGoals</t>
   </si>
   <si>
-    <t>Odd_double_h_d</t>
-  </si>
-  <si>
-    <t>Odd_double_h_a</t>
-  </si>
-  <si>
-    <t>Odd_double_d_a</t>
-  </si>
-  <si>
-    <t>Cantos_totais</t>
-  </si>
-  <si>
-    <t>odds_corners_over_75</t>
-  </si>
-  <si>
-    <t>odds_corners_over_85</t>
-  </si>
-  <si>
-    <t>odds_corners_over_95</t>
-  </si>
-  <si>
-    <t>odds_corners_over_105</t>
-  </si>
-  <si>
-    <t>odds_corners_over_115</t>
-  </si>
-  <si>
-    <t>odds_corners_under_75</t>
-  </si>
-  <si>
-    <t>odds_corners_under_85</t>
-  </si>
-  <si>
-    <t>odds_corners_under_95</t>
-  </si>
-  <si>
-    <t>odds_corners_under_105</t>
-  </si>
-  <si>
-    <t>odds_corners_under_115</t>
-  </si>
-  <si>
-    <t>odds_dnb_1</t>
-  </si>
-  <si>
-    <t>odds_dnb_2</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_1</t>
-  </si>
-  <si>
-    <t>odds_team_to_score_first_2</t>
-  </si>
-  <si>
     <t>DateTime</t>
   </si>
   <si>
@@ -220,6 +166,9 @@
     <t>16:30</t>
   </si>
   <si>
+    <t>18:00</t>
+  </si>
+  <si>
     <t>19:00</t>
   </si>
   <si>
@@ -241,27 +190,27 @@
     <t>Serbia SuperLiga</t>
   </si>
   <si>
+    <t>Iceland Úrvalsdeild</t>
+  </si>
+  <si>
     <t>Jordan Jordanian Pro League</t>
   </si>
   <si>
     <t>Serbia Prva Liga</t>
   </si>
   <si>
-    <t>Iceland Úrvalsdeild</t>
-  </si>
-  <si>
     <t>Saudi Arabia Professional League</t>
   </si>
   <si>
     <t>Netherlands Eredivisie</t>
   </si>
   <si>
+    <t>Spain La Liga</t>
+  </si>
+  <si>
     <t>Sweden Allsvenskan</t>
   </si>
   <si>
-    <t>Spain La Liga</t>
-  </si>
-  <si>
     <t>Algeria Ligue 1</t>
   </si>
   <si>
@@ -277,6 +226,9 @@
     <t>England EFL League One</t>
   </si>
   <si>
+    <t>Jamaica Jamaica National Premier League</t>
+  </si>
+  <si>
     <t>South America Copa Libertadores</t>
   </si>
   <si>
@@ -301,66 +253,66 @@
     <t>Spartak Subotica</t>
   </si>
   <si>
+    <t>Jedinstvo Ub</t>
+  </si>
+  <si>
+    <t>ÍBV</t>
+  </si>
+  <si>
     <t>Ma'an</t>
   </si>
   <si>
+    <t>Gareji</t>
+  </si>
+  <si>
     <t>Javor Ivanjica</t>
   </si>
   <si>
-    <t>Gareji</t>
-  </si>
-  <si>
-    <t>ÍBV</t>
-  </si>
-  <si>
-    <t>Jedinstvo Ub</t>
-  </si>
-  <si>
     <t>Al Orubah</t>
   </si>
   <si>
     <t>AZ</t>
   </si>
   <si>
+    <t>Torpedo Kutaisi</t>
+  </si>
+  <si>
+    <t>CA Osasuna</t>
+  </si>
+  <si>
+    <t>Värnamo</t>
+  </si>
+  <si>
+    <t>Leganés</t>
+  </si>
+  <si>
+    <t>GAIS</t>
+  </si>
+  <si>
+    <t>Paradou AC</t>
+  </si>
+  <si>
+    <t>Norrköping</t>
+  </si>
+  <si>
     <t>Djurgården</t>
   </si>
   <si>
-    <t>Värnamo</t>
-  </si>
-  <si>
-    <t>GAIS</t>
-  </si>
-  <si>
-    <t>Norrköping</t>
-  </si>
-  <si>
-    <t>Leganés</t>
-  </si>
-  <si>
-    <t>Paradou AC</t>
-  </si>
-  <si>
-    <t>Torpedo Kutaisi</t>
-  </si>
-  <si>
-    <t>CA Osasuna</t>
+    <t>Al Taawon</t>
   </si>
   <si>
     <t>Roda JC</t>
   </si>
   <si>
-    <t>Al Taawon</t>
-  </si>
-  <si>
     <t>Lokeren-Temse</t>
   </si>
   <si>
+    <t>Club Brugge</t>
+  </si>
+  <si>
     <t>Patro Eisden</t>
   </si>
   <si>
-    <t>Club Brugge</t>
-  </si>
-  <si>
     <t>Stevenage</t>
   </si>
   <si>
@@ -370,21 +322,21 @@
     <t>Afturelding</t>
   </si>
   <si>
+    <t>Atlético Madrid</t>
+  </si>
+  <si>
     <t>Real Betis</t>
   </si>
   <si>
-    <t>Atlético Madrid</t>
+    <t>Cavalier</t>
+  </si>
+  <si>
+    <t>Central Córdoba SdE</t>
   </si>
   <si>
     <t>Bolívar</t>
   </si>
   <si>
-    <t>Chicago Fire II</t>
-  </si>
-  <si>
-    <t>Central Córdoba SdE</t>
-  </si>
-  <si>
     <t>Bahia</t>
   </si>
   <si>
@@ -406,66 +358,66 @@
     <t>Napredak</t>
   </si>
   <si>
+    <t>Čukarički</t>
+  </si>
+  <si>
+    <t>Fram</t>
+  </si>
+  <si>
     <t>Shabab Al Ordon</t>
   </si>
   <si>
+    <t>Dila</t>
+  </si>
+  <si>
     <t>Mačva Šabac</t>
   </si>
   <si>
-    <t>Dila</t>
-  </si>
-  <si>
-    <t>Fram</t>
-  </si>
-  <si>
-    <t>Čukarički</t>
-  </si>
-  <si>
     <t>Al Feiha</t>
   </si>
   <si>
     <t>NAC Breda</t>
   </si>
   <si>
+    <t>Gagra</t>
+  </si>
+  <si>
+    <t>Sevilla FC</t>
+  </si>
+  <si>
+    <t>AIK</t>
+  </si>
+  <si>
+    <t>Girona FC</t>
+  </si>
+  <si>
+    <t>Brommapojkarna</t>
+  </si>
+  <si>
+    <t>ES Sétif</t>
+  </si>
+  <si>
+    <t>IFK Göteborg</t>
+  </si>
+  <si>
     <t>Öster</t>
   </si>
   <si>
-    <t>AIK</t>
-  </si>
-  <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
-    <t>IFK Göteborg</t>
-  </si>
-  <si>
-    <t>Girona FC</t>
-  </si>
-  <si>
-    <t>ES Sétif</t>
-  </si>
-  <si>
-    <t>Gagra</t>
-  </si>
-  <si>
-    <t>Sevilla FC</t>
+    <t>Al Raed</t>
   </si>
   <si>
     <t>ADO Den Haag</t>
   </si>
   <si>
-    <t>Al Raed</t>
-  </si>
-  <si>
     <t>RWDM</t>
   </si>
   <si>
+    <t>Union Saint-Gilloise</t>
+  </si>
+  <si>
     <t>Waasland-Beveren</t>
   </si>
   <si>
-    <t>Union Saint-Gilloise</t>
-  </si>
-  <si>
     <t>Birmingham City</t>
   </si>
   <si>
@@ -475,21 +427,21 @@
     <t>Víkingur Reykjavík</t>
   </si>
   <si>
+    <t>Rayo Vallecano</t>
+  </si>
+  <si>
     <t>Real Valladolid</t>
   </si>
   <si>
-    <t>Rayo Vallecano</t>
+    <t>Mount Pleasant Academy FC</t>
+  </si>
+  <si>
+    <t>Deportivo Táchira</t>
   </si>
   <si>
     <t>Palmeiras</t>
   </si>
   <si>
-    <t>New England II</t>
-  </si>
-  <si>
-    <t>Deportivo Táchira</t>
-  </si>
-  <si>
     <t>Atlético Nacional</t>
   </si>
   <si>
@@ -505,54 +457,51 @@
     <t>complete</t>
   </si>
   <si>
-    <t>incomplete</t>
-  </si>
-  <si>
     <t>[]</t>
   </si>
   <si>
     <t>['43', '78']</t>
   </si>
   <si>
+    <t>['4', '9', '25', '28']</t>
+  </si>
+  <si>
+    <t>['10', '24', '81']</t>
+  </si>
+  <si>
     <t>['-1', '-1']</t>
   </si>
   <si>
-    <t>['10', '24', '81']</t>
-  </si>
-  <si>
-    <t>['4', '9', '25', '28']</t>
-  </si>
-  <si>
     <t>['11', '18']</t>
   </si>
   <si>
     <t>['90+7']</t>
   </si>
   <si>
+    <t>['25']</t>
+  </si>
+  <si>
+    <t>['80']</t>
+  </si>
+  <si>
+    <t>['90+2']</t>
+  </si>
+  <si>
+    <t>['58']</t>
+  </si>
+  <si>
+    <t>['41', '45+1']</t>
+  </si>
+  <si>
     <t>['87']</t>
   </si>
   <si>
-    <t>['80']</t>
-  </si>
-  <si>
-    <t>['58']</t>
-  </si>
-  <si>
-    <t>['41', '45+1']</t>
-  </si>
-  <si>
-    <t>['90+2']</t>
-  </si>
-  <si>
-    <t>['25']</t>
+    <t>['30', '40', '45+6', '49']</t>
   </si>
   <si>
     <t>['90+5']</t>
   </si>
   <si>
-    <t>['30', '40', '45+6', '49']</t>
-  </si>
-  <si>
     <t>['10', '14']</t>
   </si>
   <si>
@@ -565,18 +514,21 @@
     <t>['67']</t>
   </si>
   <si>
+    <t>['3', '45', '77']</t>
+  </si>
+  <si>
     <t>['17', '64', '66', '84', '90']</t>
   </si>
   <si>
-    <t>['3', '45', '77']</t>
+    <t>['11', '90+6']</t>
+  </si>
+  <si>
+    <t>['4', '19']</t>
   </si>
   <si>
     <t>['56', '69']</t>
   </si>
   <si>
-    <t>['4', '19']</t>
-  </si>
-  <si>
     <t>['71']</t>
   </si>
   <si>
@@ -592,18 +544,18 @@
     <t>['52']</t>
   </si>
   <si>
+    <t>['15']</t>
+  </si>
+  <si>
+    <t>['41']</t>
+  </si>
+  <si>
     <t>['68']</t>
   </si>
   <si>
     <t>['-1']</t>
   </si>
   <si>
-    <t>['41']</t>
-  </si>
-  <si>
-    <t>['15']</t>
-  </si>
-  <si>
     <t>['61', '90+6']</t>
   </si>
   <si>
@@ -613,34 +565,37 @@
     <t>['42', '87']</t>
   </si>
   <si>
+    <t>['54']</t>
+  </si>
+  <si>
     <t>['26']</t>
   </si>
   <si>
     <t>['61', '76', '85']</t>
   </si>
   <si>
-    <t>['54']</t>
+    <t>['22', '54', '74']</t>
   </si>
   <si>
     <t>['29']</t>
   </si>
   <si>
-    <t>['22', '54', '74']</t>
+    <t>['34']</t>
   </si>
   <si>
     <t>['38', '73']</t>
   </si>
   <si>
-    <t>['34']</t>
-  </si>
-  <si>
     <t>['11', '53', '57']</t>
   </si>
   <si>
+    <t>['24']</t>
+  </si>
+  <si>
+    <t>['37']</t>
+  </si>
+  <si>
     <t>['19', '45', '73']</t>
-  </si>
-  <si>
-    <t>['37']</t>
   </si>
   <si>
     <t>['16', '45+1']</t>
@@ -1013,10 +968,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:BD36"/>
+  <dimension ref="A1:AL36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:56">
+    <row r="1" spans="1:38">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,79 +1086,25 @@
       <c r="AL1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="AM1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" s="1" t="s">
-        <v>55</v>
-      </c>
     </row>
-    <row r="2" spans="1:56">
+    <row r="2" spans="1:38">
       <c r="A2" s="2">
         <v>45771</v>
       </c>
       <c r="B2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="F2" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1218,7 +1119,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L2">
         <v>1.72</v>
@@ -1293,87 +1194,33 @@
         <v>1.1</v>
       </c>
       <c r="AJ2" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK2" t="s">
-        <v>190</v>
-      </c>
-      <c r="AL2">
-        <v>1.22</v>
-      </c>
-      <c r="AM2">
-        <v>1.21</v>
-      </c>
-      <c r="AN2">
-        <v>1.77</v>
-      </c>
-      <c r="AO2">
-        <v>18</v>
-      </c>
-      <c r="AP2">
-        <v>0</v>
-      </c>
-      <c r="AQ2">
-        <v>0</v>
-      </c>
-      <c r="AR2">
-        <v>0</v>
-      </c>
-      <c r="AS2">
-        <v>0</v>
-      </c>
-      <c r="AT2">
-        <v>0</v>
-      </c>
-      <c r="AU2">
-        <v>0</v>
-      </c>
-      <c r="AV2">
-        <v>0</v>
-      </c>
-      <c r="AW2">
-        <v>0</v>
-      </c>
-      <c r="AX2">
-        <v>0</v>
-      </c>
-      <c r="AY2">
-        <v>0</v>
-      </c>
-      <c r="AZ2">
-        <v>0</v>
-      </c>
-      <c r="BA2">
-        <v>0</v>
-      </c>
-      <c r="BB2">
-        <v>1.62</v>
-      </c>
-      <c r="BC2">
-        <v>2.35</v>
-      </c>
-      <c r="BD2" s="3">
+        <v>174</v>
+      </c>
+      <c r="AL2" s="3">
         <v>45771.375</v>
       </c>
     </row>
-    <row r="3" spans="1:56">
+    <row r="3" spans="1:38">
       <c r="A3" s="2">
         <v>45771</v>
       </c>
       <c r="B3" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>73</v>
+        <v>56</v>
       </c>
       <c r="D3" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="F3" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1388,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L3">
         <v>5.14</v>
@@ -1463,87 +1310,33 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK3" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL3">
-        <v>0</v>
-      </c>
-      <c r="AM3">
-        <v>0</v>
-      </c>
-      <c r="AN3">
-        <v>0</v>
-      </c>
-      <c r="AO3">
-        <v>10</v>
-      </c>
-      <c r="AP3">
-        <v>0</v>
-      </c>
-      <c r="AQ3">
-        <v>0</v>
-      </c>
-      <c r="AR3">
-        <v>0</v>
-      </c>
-      <c r="AS3">
-        <v>0</v>
-      </c>
-      <c r="AT3">
-        <v>0</v>
-      </c>
-      <c r="AU3">
-        <v>0</v>
-      </c>
-      <c r="AV3">
-        <v>0</v>
-      </c>
-      <c r="AW3">
-        <v>0</v>
-      </c>
-      <c r="AX3">
-        <v>0</v>
-      </c>
-      <c r="AY3">
-        <v>0</v>
-      </c>
-      <c r="AZ3">
-        <v>0</v>
-      </c>
-      <c r="BA3">
-        <v>0</v>
-      </c>
-      <c r="BB3">
-        <v>4</v>
-      </c>
-      <c r="BC3">
-        <v>1.29</v>
-      </c>
-      <c r="BD3" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL3" s="3">
         <v>45771.5</v>
       </c>
     </row>
-    <row r="4" spans="1:56">
+    <row r="4" spans="1:38">
       <c r="A4" s="2">
         <v>45771</v>
       </c>
       <c r="B4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" t="s">
         <v>57</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>74</v>
       </c>
-      <c r="D4" t="s">
-        <v>90</v>
-      </c>
       <c r="E4" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="F4" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1558,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L4">
         <v>2.14</v>
@@ -1633,427 +1426,265 @@
         <v>1</v>
       </c>
       <c r="AJ4" t="s">
-        <v>165</v>
+        <v>148</v>
       </c>
       <c r="AK4" t="s">
-        <v>191</v>
-      </c>
-      <c r="AL4">
-        <v>1.25</v>
-      </c>
-      <c r="AM4">
-        <v>1.33</v>
-      </c>
-      <c r="AN4">
-        <v>1.65</v>
-      </c>
-      <c r="AO4">
-        <v>11</v>
-      </c>
-      <c r="AP4">
-        <v>0</v>
-      </c>
-      <c r="AQ4">
-        <v>0</v>
-      </c>
-      <c r="AR4">
-        <v>0</v>
-      </c>
-      <c r="AS4">
-        <v>0</v>
-      </c>
-      <c r="AT4">
-        <v>0</v>
-      </c>
-      <c r="AU4">
-        <v>0</v>
-      </c>
-      <c r="AV4">
-        <v>0</v>
-      </c>
-      <c r="AW4">
-        <v>0</v>
-      </c>
-      <c r="AX4">
-        <v>0</v>
-      </c>
-      <c r="AY4">
-        <v>0</v>
-      </c>
-      <c r="AZ4">
-        <v>0</v>
-      </c>
-      <c r="BA4">
-        <v>0</v>
-      </c>
-      <c r="BB4">
-        <v>1.73</v>
-      </c>
-      <c r="BC4">
-        <v>2.63</v>
-      </c>
-      <c r="BD4" s="3">
+        <v>175</v>
+      </c>
+      <c r="AL4" s="3">
         <v>45771.5</v>
       </c>
     </row>
-    <row r="5" spans="1:56">
+    <row r="5" spans="1:38">
       <c r="A5" s="2">
         <v>45771</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H5">
         <v>1</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L5">
-        <v>3.9</v>
+        <v>5.7</v>
       </c>
       <c r="M5">
-        <v>3.35</v>
+        <v>3.72</v>
       </c>
       <c r="N5">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="O5">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Q5">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="R5">
         <v>1.4</v>
       </c>
       <c r="S5">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="T5">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="U5">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="V5">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="W5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X5">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y5">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="Z5">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AA5">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="AB5">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC5">
-        <v>1.99</v>
+        <v>1.87</v>
       </c>
       <c r="AD5">
-        <v>2.77</v>
+        <v>3.1</v>
       </c>
       <c r="AE5">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AF5">
+        <v>1.91</v>
+      </c>
+      <c r="AG5">
         <v>1.8</v>
       </c>
-      <c r="AG5">
-        <v>1.91</v>
-      </c>
       <c r="AH5">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AI5">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="AJ5" t="s">
-        <v>164</v>
+        <v>149</v>
       </c>
       <c r="AK5" t="s">
-        <v>192</v>
-      </c>
-      <c r="AL5">
-        <v>1.25</v>
-      </c>
-      <c r="AM5">
-        <v>0</v>
-      </c>
-      <c r="AN5">
-        <v>1.17</v>
-      </c>
-      <c r="AO5">
-        <v>12</v>
-      </c>
-      <c r="AP5">
-        <v>0</v>
-      </c>
-      <c r="AQ5">
-        <v>1.82</v>
-      </c>
-      <c r="AR5">
-        <v>0</v>
-      </c>
-      <c r="AS5">
-        <v>0</v>
-      </c>
-      <c r="AT5">
-        <v>0</v>
-      </c>
-      <c r="AU5">
-        <v>0</v>
-      </c>
-      <c r="AV5">
-        <v>1.98</v>
-      </c>
-      <c r="AW5">
-        <v>0</v>
-      </c>
-      <c r="AX5">
-        <v>0</v>
-      </c>
-      <c r="AY5">
-        <v>0</v>
-      </c>
-      <c r="AZ5">
-        <v>0</v>
-      </c>
-      <c r="BA5">
-        <v>0</v>
-      </c>
-      <c r="BB5">
-        <v>2.3</v>
-      </c>
-      <c r="BC5">
-        <v>1.73</v>
-      </c>
-      <c r="BD5" s="3">
+        <v>176</v>
+      </c>
+      <c r="AL5" s="3">
         <v>45771.54166666666</v>
       </c>
     </row>
-    <row r="6" spans="1:56">
+    <row r="6" spans="1:38">
       <c r="A6" s="2">
         <v>45771</v>
       </c>
       <c r="B6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" t="s">
         <v>58</v>
       </c>
-      <c r="C6" t="s">
-        <v>76</v>
-      </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>80</v>
       </c>
       <c r="F6" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G6">
+        <v>3</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
         <v>2</v>
       </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
       <c r="J6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L6">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="M6">
-        <v>3.13</v>
+        <v>3.4</v>
       </c>
       <c r="N6">
-        <v>3.63</v>
+        <v>2.55</v>
       </c>
       <c r="O6">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="P6">
         <v>0</v>
       </c>
       <c r="Q6">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U6">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="V6">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="W6">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z6">
+        <v>1.18</v>
+      </c>
+      <c r="AA6">
+        <v>4.33</v>
+      </c>
+      <c r="AB6">
+        <v>1.57</v>
+      </c>
+      <c r="AC6">
+        <v>2.25</v>
+      </c>
+      <c r="AD6">
+        <v>2.4</v>
+      </c>
+      <c r="AE6">
         <v>1.5</v>
       </c>
-      <c r="AA6">
-        <v>2.3</v>
-      </c>
-      <c r="AB6">
-        <v>2.93</v>
-      </c>
-      <c r="AC6">
-        <v>1.33</v>
-      </c>
-      <c r="AD6">
-        <v>2.45</v>
-      </c>
-      <c r="AE6">
-        <v>1.47</v>
-      </c>
       <c r="AF6">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG6">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AI6">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AJ6" t="s">
-        <v>166</v>
+        <v>150</v>
       </c>
       <c r="AK6" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL6">
-        <v>0</v>
-      </c>
-      <c r="AM6">
-        <v>0</v>
-      </c>
-      <c r="AN6">
-        <v>0</v>
-      </c>
-      <c r="AO6">
-        <v>8</v>
-      </c>
-      <c r="AP6">
-        <v>0</v>
-      </c>
-      <c r="AQ6">
-        <v>0</v>
-      </c>
-      <c r="AR6">
-        <v>0</v>
-      </c>
-      <c r="AS6">
-        <v>0</v>
-      </c>
-      <c r="AT6">
-        <v>0</v>
-      </c>
-      <c r="AU6">
-        <v>0</v>
-      </c>
-      <c r="AV6">
-        <v>0</v>
-      </c>
-      <c r="AW6">
-        <v>0</v>
-      </c>
-      <c r="AX6">
-        <v>0</v>
-      </c>
-      <c r="AY6">
-        <v>0</v>
-      </c>
-      <c r="AZ6">
-        <v>0</v>
-      </c>
-      <c r="BA6">
-        <v>0</v>
-      </c>
-      <c r="BB6">
-        <v>1.67</v>
-      </c>
-      <c r="BC6">
-        <v>2.88</v>
-      </c>
-      <c r="BD6" s="3">
+        <v>177</v>
+      </c>
+      <c r="AL6" s="3">
         <v>45771.54166666666</v>
       </c>
     </row>
-    <row r="7" spans="1:56">
+    <row r="7" spans="1:38">
       <c r="A7" s="2">
         <v>45771</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D7" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="F7" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -2068,502 +1699,340 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L7">
-        <v>6</v>
+        <v>3.9</v>
       </c>
       <c r="M7">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="N7">
-        <v>1.48</v>
+        <v>1.84</v>
       </c>
       <c r="O7">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="P7">
         <v>0</v>
       </c>
       <c r="Q7">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U7">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X7">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="Z7">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AA7">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AB7">
+        <v>1.85</v>
+      </c>
+      <c r="AC7">
+        <v>1.99</v>
+      </c>
+      <c r="AD7">
+        <v>2.77</v>
+      </c>
+      <c r="AE7">
+        <v>1.38</v>
+      </c>
+      <c r="AF7">
         <v>1.8</v>
       </c>
-      <c r="AC7">
-        <v>1.83</v>
-      </c>
-      <c r="AD7">
-        <v>3.2</v>
-      </c>
-      <c r="AE7">
-        <v>1.25</v>
-      </c>
-      <c r="AF7">
-        <v>0</v>
-      </c>
       <c r="AG7">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH7">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AI7">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AJ7" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK7" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL7">
-        <v>0</v>
-      </c>
-      <c r="AM7">
-        <v>0</v>
-      </c>
-      <c r="AN7">
-        <v>0</v>
-      </c>
-      <c r="AO7">
-        <v>-1</v>
-      </c>
-      <c r="AP7">
-        <v>0</v>
-      </c>
-      <c r="AQ7">
-        <v>0</v>
-      </c>
-      <c r="AR7">
-        <v>0</v>
-      </c>
-      <c r="AS7">
-        <v>0</v>
-      </c>
-      <c r="AT7">
-        <v>0</v>
-      </c>
-      <c r="AU7">
-        <v>0</v>
-      </c>
-      <c r="AV7">
-        <v>0</v>
-      </c>
-      <c r="AW7">
-        <v>0</v>
-      </c>
-      <c r="AX7">
-        <v>0</v>
-      </c>
-      <c r="AY7">
-        <v>0</v>
-      </c>
-      <c r="AZ7">
-        <v>0</v>
-      </c>
-      <c r="BA7">
-        <v>0</v>
-      </c>
-      <c r="BB7">
-        <v>3.6</v>
-      </c>
-      <c r="BC7">
-        <v>1.33</v>
-      </c>
-      <c r="BD7" s="3">
+        <v>178</v>
+      </c>
+      <c r="AL7" s="3">
         <v>45771.54166666666</v>
       </c>
     </row>
-    <row r="8" spans="1:56">
+    <row r="8" spans="1:38">
       <c r="A8" s="2">
         <v>45771</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>77</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E8" t="s">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="F8" t="s">
-        <v>133</v>
+        <v>117</v>
       </c>
       <c r="G8">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L8">
-        <v>2.5</v>
+        <v>6</v>
       </c>
       <c r="M8">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N8">
-        <v>2.55</v>
+        <v>1.48</v>
       </c>
       <c r="O8">
-        <v>1.91</v>
+        <v>3.6</v>
       </c>
       <c r="P8">
         <v>0</v>
       </c>
       <c r="Q8">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="R8">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S8">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="V8">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="W8">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="Z8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AA8">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AB8">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AC8">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AD8">
-        <v>2.4</v>
+        <v>3.2</v>
       </c>
       <c r="AE8">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AF8">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG8">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AH8">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AI8">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="AK8" t="s">
-        <v>194</v>
-      </c>
-      <c r="AL8">
-        <v>1.26</v>
-      </c>
-      <c r="AM8">
-        <v>0</v>
-      </c>
-      <c r="AN8">
-        <v>1.5</v>
-      </c>
-      <c r="AO8">
-        <v>7</v>
-      </c>
-      <c r="AP8">
-        <v>1.12</v>
-      </c>
-      <c r="AQ8">
-        <v>1.25</v>
-      </c>
-      <c r="AR8">
-        <v>1.54</v>
-      </c>
-      <c r="AS8">
-        <v>1.7</v>
-      </c>
-      <c r="AT8">
-        <v>2.1</v>
-      </c>
-      <c r="AU8">
-        <v>4.95</v>
-      </c>
-      <c r="AV8">
-        <v>3.6</v>
-      </c>
-      <c r="AW8">
-        <v>2.62</v>
-      </c>
-      <c r="AX8">
-        <v>2.07</v>
-      </c>
-      <c r="AY8">
-        <v>1.65</v>
-      </c>
-      <c r="AZ8">
-        <v>0</v>
-      </c>
-      <c r="BA8">
-        <v>0</v>
-      </c>
-      <c r="BB8">
-        <v>1.91</v>
-      </c>
-      <c r="BC8">
-        <v>1.91</v>
-      </c>
-      <c r="BD8" s="3">
+        <v>179</v>
+      </c>
+      <c r="AL8" s="3">
         <v>45771.54166666666</v>
       </c>
     </row>
-    <row r="9" spans="1:56">
+    <row r="9" spans="1:38">
       <c r="A9" s="2">
         <v>45771</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
+        <v>60</v>
+      </c>
+      <c r="D9" t="s">
         <v>74</v>
       </c>
-      <c r="D9" t="s">
-        <v>90</v>
-      </c>
       <c r="E9" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="F9" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="G9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H9">
         <v>1</v>
       </c>
       <c r="I9">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L9">
-        <v>5.7</v>
+        <v>2.11</v>
       </c>
       <c r="M9">
-        <v>3.72</v>
+        <v>3.13</v>
       </c>
       <c r="N9">
-        <v>1.6</v>
+        <v>3.63</v>
       </c>
       <c r="O9">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="P9">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q9">
-        <v>1.4</v>
+        <v>2.88</v>
       </c>
       <c r="R9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S9">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T9">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U9">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X9">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y9">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Z9">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AA9">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AB9">
-        <v>1.87</v>
+        <v>2.93</v>
       </c>
       <c r="AC9">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AD9">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AE9">
-        <v>1.33</v>
+        <v>1.47</v>
       </c>
       <c r="AF9">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG9">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AH9">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AI9">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="AK9" t="s">
-        <v>195</v>
-      </c>
-      <c r="AL9">
-        <v>2.3</v>
-      </c>
-      <c r="AM9">
-        <v>1.2</v>
-      </c>
-      <c r="AN9">
-        <v>1.1</v>
-      </c>
-      <c r="AO9">
-        <v>12</v>
-      </c>
-      <c r="AP9">
-        <v>0</v>
-      </c>
-      <c r="AQ9">
-        <v>0</v>
-      </c>
-      <c r="AR9">
-        <v>0</v>
-      </c>
-      <c r="AS9">
-        <v>0</v>
-      </c>
-      <c r="AT9">
-        <v>0</v>
-      </c>
-      <c r="AU9">
-        <v>0</v>
-      </c>
-      <c r="AV9">
-        <v>0</v>
-      </c>
-      <c r="AW9">
-        <v>0</v>
-      </c>
-      <c r="AX9">
-        <v>0</v>
-      </c>
-      <c r="AY9">
-        <v>0</v>
-      </c>
-      <c r="AZ9">
-        <v>0</v>
-      </c>
-      <c r="BA9">
-        <v>0</v>
-      </c>
-      <c r="BB9">
-        <v>3.25</v>
-      </c>
-      <c r="BC9">
-        <v>1.4</v>
-      </c>
-      <c r="BD9" s="3">
+        <v>179</v>
+      </c>
+      <c r="AL9" s="3">
         <v>45771.54166666666</v>
       </c>
     </row>
-    <row r="10" spans="1:56">
+    <row r="10" spans="1:38">
       <c r="A10" s="2">
         <v>45771</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="C10" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="F10" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -2578,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L10">
         <v>2.95</v>
@@ -2653,87 +2122,33 @@
         <v>1.05</v>
       </c>
       <c r="AJ10" t="s">
-        <v>169</v>
+        <v>152</v>
       </c>
       <c r="AK10" t="s">
-        <v>196</v>
-      </c>
-      <c r="AL10">
-        <v>1.55</v>
-      </c>
-      <c r="AM10">
-        <v>1.28</v>
-      </c>
-      <c r="AN10">
-        <v>1.38</v>
-      </c>
-      <c r="AO10">
-        <v>10</v>
-      </c>
-      <c r="AP10">
-        <v>1.42</v>
-      </c>
-      <c r="AQ10">
-        <v>1.74</v>
-      </c>
-      <c r="AR10">
-        <v>2.18</v>
-      </c>
-      <c r="AS10">
-        <v>2.85</v>
-      </c>
-      <c r="AT10">
-        <v>3.8</v>
-      </c>
-      <c r="AU10">
-        <v>2.55</v>
-      </c>
-      <c r="AV10">
-        <v>1.92</v>
-      </c>
-      <c r="AW10">
-        <v>1.56</v>
-      </c>
-      <c r="AX10">
-        <v>1.34</v>
-      </c>
-      <c r="AY10">
-        <v>1.19</v>
-      </c>
-      <c r="AZ10">
-        <v>0</v>
-      </c>
-      <c r="BA10">
-        <v>0</v>
-      </c>
-      <c r="BB10">
-        <v>2.2</v>
-      </c>
-      <c r="BC10">
-        <v>1.81</v>
-      </c>
-      <c r="BD10" s="3">
+        <v>180</v>
+      </c>
+      <c r="AL10" s="3">
         <v>45771.5625</v>
       </c>
     </row>
-    <row r="11" spans="1:56">
+    <row r="11" spans="1:38">
       <c r="A11" s="2">
         <v>45771</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D11" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>136</v>
+        <v>120</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -2748,7 +2163,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L11">
         <v>1.45</v>
@@ -2823,93 +2238,39 @@
         <v>1.15</v>
       </c>
       <c r="AJ11" t="s">
-        <v>170</v>
+        <v>153</v>
       </c>
       <c r="AK11" t="s">
-        <v>197</v>
-      </c>
-      <c r="AL11">
-        <v>1.08</v>
-      </c>
-      <c r="AM11">
-        <v>1.14</v>
-      </c>
-      <c r="AN11">
-        <v>2.88</v>
-      </c>
-      <c r="AO11">
-        <v>14</v>
-      </c>
-      <c r="AP11">
-        <v>1.23</v>
-      </c>
-      <c r="AQ11">
-        <v>1.45</v>
-      </c>
-      <c r="AR11">
-        <v>1.77</v>
-      </c>
-      <c r="AS11">
-        <v>2.28</v>
-      </c>
-      <c r="AT11">
-        <v>3.04</v>
-      </c>
-      <c r="AU11">
-        <v>3.42</v>
-      </c>
-      <c r="AV11">
-        <v>2.48</v>
-      </c>
-      <c r="AW11">
-        <v>1.95</v>
-      </c>
-      <c r="AX11">
-        <v>1.53</v>
-      </c>
-      <c r="AY11">
-        <v>1.29</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>1.29</v>
-      </c>
-      <c r="BC11">
-        <v>3.75</v>
-      </c>
-      <c r="BD11" s="3">
+        <v>181</v>
+      </c>
+      <c r="AL11" s="3">
         <v>45771.57291666666</v>
       </c>
     </row>
-    <row r="12" spans="1:56">
+    <row r="12" spans="1:38">
       <c r="A12" s="2">
         <v>45771</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F12" t="s">
-        <v>137</v>
+        <v>121</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -2918,338 +2279,230 @@
         <v>0</v>
       </c>
       <c r="K12" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L12">
+        <v>2.2</v>
+      </c>
+      <c r="M12">
+        <v>3.5</v>
+      </c>
+      <c r="N12">
+        <v>2.8</v>
+      </c>
+      <c r="O12">
+        <v>3.25</v>
+      </c>
+      <c r="P12">
+        <v>0</v>
+      </c>
+      <c r="Q12">
         <v>1.44</v>
       </c>
-      <c r="M12">
-        <v>4.7</v>
-      </c>
-      <c r="N12">
-        <v>6.2</v>
-      </c>
-      <c r="O12">
-        <v>1.3</v>
-      </c>
-      <c r="P12">
-        <v>13</v>
-      </c>
-      <c r="Q12">
-        <v>3.4</v>
-      </c>
       <c r="R12">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S12">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T12">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="U12">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V12">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="W12">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="X12">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12">
-        <v>14.4</v>
+        <v>0</v>
       </c>
       <c r="Z12">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AA12">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AB12">
-        <v>1.53</v>
+        <v>1.85</v>
       </c>
       <c r="AC12">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="AD12">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AE12">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AF12">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG12">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH12">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AI12">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="AK12" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL12">
-        <v>1.11</v>
-      </c>
-      <c r="AM12">
-        <v>1.14</v>
-      </c>
-      <c r="AN12">
-        <v>2.75</v>
-      </c>
-      <c r="AO12">
-        <v>18</v>
-      </c>
-      <c r="AP12">
-        <v>1.09</v>
-      </c>
-      <c r="AQ12">
-        <v>1.22</v>
-      </c>
-      <c r="AR12">
-        <v>1.43</v>
-      </c>
-      <c r="AS12">
-        <v>1.77</v>
-      </c>
-      <c r="AT12">
-        <v>2.15</v>
-      </c>
-      <c r="AU12">
-        <v>5.25</v>
-      </c>
-      <c r="AV12">
-        <v>3.5</v>
-      </c>
-      <c r="AW12">
-        <v>2.54</v>
-      </c>
-      <c r="AX12">
-        <v>1.95</v>
-      </c>
-      <c r="AY12">
-        <v>1.59</v>
-      </c>
-      <c r="AZ12">
-        <v>0</v>
-      </c>
-      <c r="BA12">
-        <v>0</v>
-      </c>
-      <c r="BB12">
-        <v>1.3</v>
-      </c>
-      <c r="BC12">
-        <v>3.4</v>
-      </c>
-      <c r="BD12" s="3">
+        <v>179</v>
+      </c>
+      <c r="AL12" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="13" spans="1:56">
+    <row r="13" spans="1:38">
       <c r="A13" s="2">
         <v>45771</v>
       </c>
       <c r="B13" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F13" t="s">
-        <v>138</v>
+        <v>122</v>
       </c>
       <c r="G13">
         <v>1</v>
       </c>
       <c r="H13">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L13">
-        <v>3.08</v>
+        <v>2.55</v>
       </c>
       <c r="M13">
-        <v>3.47</v>
+        <v>3</v>
       </c>
       <c r="N13">
-        <v>2.19</v>
+        <v>3</v>
       </c>
       <c r="O13">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="P13">
         <v>7</v>
       </c>
       <c r="Q13">
+        <v>2.25</v>
+      </c>
+      <c r="R13">
+        <v>1.5</v>
+      </c>
+      <c r="S13">
+        <v>2.5</v>
+      </c>
+      <c r="T13">
+        <v>3.5</v>
+      </c>
+      <c r="U13">
+        <v>1.29</v>
+      </c>
+      <c r="V13">
+        <v>10</v>
+      </c>
+      <c r="W13">
+        <v>1.06</v>
+      </c>
+      <c r="X13">
+        <v>1.09</v>
+      </c>
+      <c r="Y13">
+        <v>7</v>
+      </c>
+      <c r="Z13">
+        <v>1.44</v>
+      </c>
+      <c r="AA13">
+        <v>2.7</v>
+      </c>
+      <c r="AB13">
+        <v>2.3</v>
+      </c>
+      <c r="AC13">
+        <v>1.62</v>
+      </c>
+      <c r="AD13">
+        <v>4.33</v>
+      </c>
+      <c r="AE13">
+        <v>1.2</v>
+      </c>
+      <c r="AF13">
+        <v>1.95</v>
+      </c>
+      <c r="AG13">
         <v>1.8</v>
       </c>
-      <c r="R13">
-        <v>1.57</v>
-      </c>
-      <c r="S13">
-        <v>2.25</v>
-      </c>
-      <c r="T13">
-        <v>3.75</v>
-      </c>
-      <c r="U13">
-        <v>1.25</v>
-      </c>
-      <c r="V13">
-        <v>13</v>
-      </c>
-      <c r="W13">
-        <v>1.04</v>
-      </c>
-      <c r="X13">
-        <v>1.04</v>
-      </c>
-      <c r="Y13">
-        <v>6.8</v>
-      </c>
-      <c r="Z13">
-        <v>1.5</v>
-      </c>
-      <c r="AA13">
-        <v>2.4</v>
-      </c>
-      <c r="AB13">
-        <v>2.05</v>
-      </c>
-      <c r="AC13">
-        <v>1.61</v>
-      </c>
-      <c r="AD13">
-        <v>4.65</v>
-      </c>
-      <c r="AE13">
-        <v>1.14</v>
-      </c>
-      <c r="AF13">
-        <v>2.1</v>
-      </c>
-      <c r="AG13">
-        <v>1.67</v>
-      </c>
       <c r="AH13">
-        <v>11</v>
+        <v>8.5</v>
       </c>
       <c r="AI13">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AJ13" t="s">
-        <v>172</v>
+        <v>154</v>
       </c>
       <c r="AK13" t="s">
-        <v>198</v>
-      </c>
-      <c r="AL13">
-        <v>1.57</v>
-      </c>
-      <c r="AM13">
-        <v>1.3</v>
-      </c>
-      <c r="AN13">
-        <v>1.33</v>
-      </c>
-      <c r="AO13">
-        <v>-1</v>
-      </c>
-      <c r="AP13">
-        <v>1.21</v>
-      </c>
-      <c r="AQ13">
-        <v>1.38</v>
-      </c>
-      <c r="AR13">
-        <v>1.61</v>
-      </c>
-      <c r="AS13">
-        <v>1.96</v>
-      </c>
-      <c r="AT13">
-        <v>2.43</v>
-      </c>
-      <c r="AU13">
-        <v>3.8</v>
-      </c>
-      <c r="AV13">
-        <v>2.8</v>
-      </c>
-      <c r="AW13">
-        <v>2.15</v>
-      </c>
-      <c r="AX13">
-        <v>1.74</v>
-      </c>
-      <c r="AY13">
-        <v>1.49</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>2.4</v>
-      </c>
-      <c r="BC13">
-        <v>1.8</v>
-      </c>
-      <c r="BD13" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL13" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="14" spans="1:56">
+    <row r="14" spans="1:38">
       <c r="A14" s="2">
         <v>45771</v>
       </c>
       <c r="B14" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C14" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="F14" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="G14">
         <v>1</v>
       </c>
       <c r="H14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -3258,332 +2511,224 @@
         <v>1</v>
       </c>
       <c r="K14" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L14">
-        <v>1.91</v>
+        <v>3.08</v>
       </c>
       <c r="M14">
-        <v>3.59</v>
+        <v>3.47</v>
       </c>
       <c r="N14">
-        <v>3.74</v>
+        <v>2.19</v>
       </c>
       <c r="O14">
+        <v>2.4</v>
+      </c>
+      <c r="P14">
+        <v>7</v>
+      </c>
+      <c r="Q14">
+        <v>1.8</v>
+      </c>
+      <c r="R14">
         <v>1.57</v>
       </c>
-      <c r="P14">
-        <v>10</v>
-      </c>
-      <c r="Q14">
-        <v>2.5</v>
-      </c>
-      <c r="R14">
-        <v>1.33</v>
-      </c>
       <c r="S14">
-        <v>3.25</v>
+        <v>2.25</v>
       </c>
       <c r="T14">
-        <v>2.63</v>
+        <v>3.75</v>
       </c>
       <c r="U14">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V14">
-        <v>6.5</v>
+        <v>13</v>
       </c>
       <c r="W14">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="X14">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="Y14">
-        <v>11.8</v>
+        <v>6.8</v>
       </c>
       <c r="Z14">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AA14">
-        <v>3.84</v>
+        <v>2.4</v>
       </c>
       <c r="AB14">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AC14">
-        <v>1.94</v>
+        <v>1.61</v>
       </c>
       <c r="AD14">
-        <v>2.78</v>
+        <v>4.65</v>
       </c>
       <c r="AE14">
-        <v>1.36</v>
+        <v>1.14</v>
       </c>
       <c r="AF14">
+        <v>2.1</v>
+      </c>
+      <c r="AG14">
         <v>1.67</v>
       </c>
-      <c r="AG14">
-        <v>2.1</v>
-      </c>
       <c r="AH14">
-        <v>5.05</v>
+        <v>11</v>
       </c>
       <c r="AI14">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="AJ14" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="AK14" t="s">
-        <v>199</v>
-      </c>
-      <c r="AL14">
-        <v>1.28</v>
-      </c>
-      <c r="AM14">
-        <v>1.25</v>
-      </c>
-      <c r="AN14">
-        <v>1.8</v>
-      </c>
-      <c r="AO14">
-        <v>16</v>
-      </c>
-      <c r="AP14">
-        <v>1.1</v>
-      </c>
-      <c r="AQ14">
-        <v>1.23</v>
-      </c>
-      <c r="AR14">
-        <v>1.44</v>
-      </c>
-      <c r="AS14">
-        <v>1.77</v>
-      </c>
-      <c r="AT14">
-        <v>2.19</v>
-      </c>
-      <c r="AU14">
-        <v>5.15</v>
-      </c>
-      <c r="AV14">
-        <v>3.42</v>
-      </c>
-      <c r="AW14">
-        <v>2.51</v>
-      </c>
-      <c r="AX14">
-        <v>1.95</v>
-      </c>
-      <c r="AY14">
-        <v>1.57</v>
-      </c>
-      <c r="AZ14">
-        <v>0</v>
-      </c>
-      <c r="BA14">
-        <v>0</v>
-      </c>
-      <c r="BB14">
-        <v>1.57</v>
-      </c>
-      <c r="BC14">
-        <v>2.5</v>
-      </c>
-      <c r="BD14" s="3">
+        <v>182</v>
+      </c>
+      <c r="AL14" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:56">
+    <row r="15" spans="1:38">
       <c r="A15" s="2">
         <v>45771</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C15" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="D15" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E15" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="F15" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I15">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L15">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="M15">
-        <v>3.67</v>
+        <v>3.2</v>
       </c>
       <c r="N15">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="O15">
         <v>1.83</v>
       </c>
       <c r="P15">
+        <v>7.5</v>
+      </c>
+      <c r="Q15">
+        <v>2.2</v>
+      </c>
+      <c r="R15">
+        <v>1.5</v>
+      </c>
+      <c r="S15">
+        <v>2.5</v>
+      </c>
+      <c r="T15">
+        <v>3.4</v>
+      </c>
+      <c r="U15">
+        <v>1.3</v>
+      </c>
+      <c r="V15">
         <v>10</v>
       </c>
-      <c r="Q15">
-        <v>2.05</v>
-      </c>
-      <c r="R15">
-        <v>1.33</v>
-      </c>
-      <c r="S15">
-        <v>3.25</v>
-      </c>
-      <c r="T15">
-        <v>2.63</v>
-      </c>
-      <c r="U15">
-        <v>1.44</v>
-      </c>
-      <c r="V15">
-        <v>6.5</v>
-      </c>
       <c r="W15">
-        <v>1.11</v>
+        <v>1.06</v>
       </c>
       <c r="X15">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y15">
-        <v>12.5</v>
+        <v>7.5</v>
       </c>
       <c r="Z15">
-        <v>1.14</v>
+        <v>1.4</v>
       </c>
       <c r="AA15">
-        <v>4.4</v>
+        <v>2.88</v>
       </c>
       <c r="AB15">
-        <v>1.72</v>
+        <v>2.2</v>
       </c>
       <c r="AC15">
-        <v>2.05</v>
+        <v>1.67</v>
       </c>
       <c r="AD15">
-        <v>2.25</v>
+        <v>4.2</v>
       </c>
       <c r="AE15">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AF15">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AG15">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AH15">
-        <v>4.7</v>
+        <v>8</v>
       </c>
       <c r="AI15">
-        <v>1.13</v>
+        <v>1.07</v>
       </c>
       <c r="AJ15" t="s">
-        <v>174</v>
+        <v>156</v>
       </c>
       <c r="AK15" t="s">
-        <v>200</v>
-      </c>
-      <c r="AL15">
-        <v>1.48</v>
-      </c>
-      <c r="AM15">
-        <v>1.25</v>
-      </c>
-      <c r="AN15">
-        <v>1.48</v>
-      </c>
-      <c r="AO15">
-        <v>16</v>
-      </c>
-      <c r="AP15">
-        <v>1.15</v>
-      </c>
-      <c r="AQ15">
-        <v>1.26</v>
-      </c>
-      <c r="AR15">
-        <v>1.45</v>
-      </c>
-      <c r="AS15">
-        <v>1.71</v>
-      </c>
-      <c r="AT15">
-        <v>2.07</v>
-      </c>
-      <c r="AU15">
-        <v>4.6</v>
-      </c>
-      <c r="AV15">
-        <v>3.4</v>
-      </c>
-      <c r="AW15">
-        <v>2.55</v>
-      </c>
-      <c r="AX15">
-        <v>2</v>
-      </c>
-      <c r="AY15">
-        <v>1.67</v>
-      </c>
-      <c r="AZ15">
-        <v>0</v>
-      </c>
-      <c r="BA15">
-        <v>0</v>
-      </c>
-      <c r="BB15">
-        <v>1.83</v>
-      </c>
-      <c r="BC15">
-        <v>2.05</v>
-      </c>
-      <c r="BD15" s="3">
+        <v>183</v>
+      </c>
+      <c r="AL15" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="16" spans="1:56">
+    <row r="16" spans="1:38">
       <c r="A16" s="2">
         <v>45771</v>
       </c>
       <c r="B16" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C16" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s">
+        <v>75</v>
+      </c>
+      <c r="E16" t="s">
         <v>90</v>
       </c>
-      <c r="E16" t="s">
-        <v>106</v>
-      </c>
       <c r="F16" t="s">
-        <v>141</v>
+        <v>125</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -3595,165 +2740,111 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L16">
+        <v>1.91</v>
+      </c>
+      <c r="M16">
+        <v>3.59</v>
+      </c>
+      <c r="N16">
+        <v>3.74</v>
+      </c>
+      <c r="O16">
+        <v>1.57</v>
+      </c>
+      <c r="P16">
+        <v>10</v>
+      </c>
+      <c r="Q16">
         <v>2.5</v>
       </c>
-      <c r="M16">
-        <v>3.2</v>
-      </c>
-      <c r="N16">
-        <v>2.9</v>
-      </c>
-      <c r="O16">
-        <v>1.83</v>
-      </c>
-      <c r="P16">
-        <v>7.5</v>
-      </c>
-      <c r="Q16">
-        <v>2.2</v>
-      </c>
       <c r="R16">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="S16">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="T16">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="U16">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>6.5</v>
       </c>
       <c r="W16">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X16">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y16">
-        <v>7.5</v>
+        <v>11.8</v>
       </c>
       <c r="Z16">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="AA16">
-        <v>2.88</v>
+        <v>3.84</v>
       </c>
       <c r="AB16">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="AC16">
+        <v>1.94</v>
+      </c>
+      <c r="AD16">
+        <v>2.78</v>
+      </c>
+      <c r="AE16">
+        <v>1.36</v>
+      </c>
+      <c r="AF16">
         <v>1.67</v>
       </c>
-      <c r="AD16">
-        <v>4.2</v>
-      </c>
-      <c r="AE16">
-        <v>1.22</v>
-      </c>
-      <c r="AF16">
-        <v>1.91</v>
-      </c>
       <c r="AG16">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AH16">
-        <v>8</v>
+        <v>5.05</v>
       </c>
       <c r="AI16">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="AJ16" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="AK16" t="s">
-        <v>201</v>
-      </c>
-      <c r="AL16">
-        <v>1.42</v>
-      </c>
-      <c r="AM16">
-        <v>1.3</v>
-      </c>
-      <c r="AN16">
-        <v>1.5</v>
-      </c>
-      <c r="AO16">
-        <v>9</v>
-      </c>
-      <c r="AP16">
-        <v>1.39</v>
-      </c>
-      <c r="AQ16">
-        <v>1.73</v>
-      </c>
-      <c r="AR16">
-        <v>2.19</v>
-      </c>
-      <c r="AS16">
-        <v>2.92</v>
-      </c>
-      <c r="AT16">
-        <v>4.15</v>
-      </c>
-      <c r="AU16">
-        <v>2.67</v>
-      </c>
-      <c r="AV16">
-        <v>2</v>
-      </c>
-      <c r="AW16">
-        <v>1.57</v>
-      </c>
-      <c r="AX16">
-        <v>1.31</v>
-      </c>
-      <c r="AY16">
-        <v>1.16</v>
-      </c>
-      <c r="AZ16">
-        <v>0</v>
-      </c>
-      <c r="BA16">
-        <v>0</v>
-      </c>
-      <c r="BB16">
-        <v>1.83</v>
-      </c>
-      <c r="BC16">
-        <v>2.2</v>
-      </c>
-      <c r="BD16" s="3">
+        <v>184</v>
+      </c>
+      <c r="AL16" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="17" spans="1:56">
+    <row r="17" spans="1:38">
       <c r="A17" s="2">
         <v>45771</v>
       </c>
       <c r="B17" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C17" t="s">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="D17" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E17" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="F17" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -3768,7 +2859,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L17">
         <v>2.45</v>
@@ -3843,257 +2934,149 @@
         <v>1.02</v>
       </c>
       <c r="AJ17" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK17" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL17">
-        <v>1.3</v>
-      </c>
-      <c r="AM17">
-        <v>0</v>
-      </c>
-      <c r="AN17">
-        <v>1.5</v>
-      </c>
-      <c r="AO17">
-        <v>4</v>
-      </c>
-      <c r="AP17">
-        <v>1.67</v>
-      </c>
-      <c r="AQ17">
-        <v>2.13</v>
-      </c>
-      <c r="AR17">
-        <v>2.88</v>
-      </c>
-      <c r="AS17">
-        <v>3.78</v>
-      </c>
-      <c r="AT17">
-        <v>5.25</v>
-      </c>
-      <c r="AU17">
-        <v>2.1</v>
-      </c>
-      <c r="AV17">
-        <v>1.58</v>
-      </c>
-      <c r="AW17">
-        <v>1.32</v>
-      </c>
-      <c r="AX17">
-        <v>1.21</v>
-      </c>
-      <c r="AY17">
-        <v>1.11</v>
-      </c>
-      <c r="AZ17">
-        <v>0</v>
-      </c>
-      <c r="BA17">
-        <v>0</v>
-      </c>
-      <c r="BB17">
-        <v>1.95</v>
-      </c>
-      <c r="BC17">
-        <v>2.3</v>
-      </c>
-      <c r="BD17" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL17" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="18" spans="1:56">
+    <row r="18" spans="1:38">
       <c r="A18" s="2">
         <v>45771</v>
       </c>
       <c r="B18" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C18" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E18" t="s">
-        <v>108</v>
+        <v>92</v>
       </c>
       <c r="F18" t="s">
-        <v>143</v>
+        <v>127</v>
       </c>
       <c r="G18">
         <v>2</v>
       </c>
       <c r="H18">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J18">
         <v>0</v>
       </c>
       <c r="K18" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L18">
-        <v>2.2</v>
+        <v>2.58</v>
       </c>
       <c r="M18">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N18">
-        <v>2.8</v>
+        <v>2.44</v>
       </c>
       <c r="O18">
+        <v>1.83</v>
+      </c>
+      <c r="P18">
+        <v>10</v>
+      </c>
+      <c r="Q18">
+        <v>2.05</v>
+      </c>
+      <c r="R18">
+        <v>1.33</v>
+      </c>
+      <c r="S18">
         <v>3.25</v>
       </c>
-      <c r="P18">
-        <v>0</v>
-      </c>
-      <c r="Q18">
+      <c r="T18">
+        <v>2.63</v>
+      </c>
+      <c r="U18">
         <v>1.44</v>
       </c>
-      <c r="R18">
-        <v>0</v>
-      </c>
-      <c r="S18">
-        <v>0</v>
-      </c>
-      <c r="T18">
-        <v>0</v>
-      </c>
-      <c r="U18">
-        <v>0</v>
-      </c>
       <c r="V18">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W18">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y18">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="Z18">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AA18">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AB18">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC18">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AD18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AE18">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF18">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG18">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH18">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AI18">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AJ18" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="AK18" t="s">
-        <v>193</v>
-      </c>
-      <c r="AL18">
-        <v>0</v>
-      </c>
-      <c r="AM18">
-        <v>0</v>
-      </c>
-      <c r="AN18">
-        <v>0</v>
-      </c>
-      <c r="AO18">
-        <v>7</v>
-      </c>
-      <c r="AP18">
-        <v>0</v>
-      </c>
-      <c r="AQ18">
-        <v>0</v>
-      </c>
-      <c r="AR18">
-        <v>0</v>
-      </c>
-      <c r="AS18">
-        <v>0</v>
-      </c>
-      <c r="AT18">
-        <v>0</v>
-      </c>
-      <c r="AU18">
-        <v>0</v>
-      </c>
-      <c r="AV18">
-        <v>0</v>
-      </c>
-      <c r="AW18">
-        <v>0</v>
-      </c>
-      <c r="AX18">
-        <v>0</v>
-      </c>
-      <c r="AY18">
-        <v>0</v>
-      </c>
-      <c r="AZ18">
-        <v>0</v>
-      </c>
-      <c r="BA18">
-        <v>0</v>
-      </c>
-      <c r="BB18">
-        <v>3.25</v>
-      </c>
-      <c r="BC18">
-        <v>1.44</v>
-      </c>
-      <c r="BD18" s="3">
+        <v>185</v>
+      </c>
+      <c r="AL18" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="19" spans="1:56">
+    <row r="19" spans="1:38">
       <c r="A19" s="2">
         <v>45771</v>
       </c>
       <c r="B19" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>81</v>
+        <v>64</v>
       </c>
       <c r="D19" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="E19" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="F19" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -4102,508 +3085,346 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L19">
-        <v>2.55</v>
+        <v>1.44</v>
       </c>
       <c r="M19">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="N19">
-        <v>3</v>
+        <v>6.2</v>
       </c>
       <c r="O19">
-        <v>1.83</v>
+        <v>1.3</v>
       </c>
       <c r="P19">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="Q19">
+        <v>3.4</v>
+      </c>
+      <c r="R19">
+        <v>1.29</v>
+      </c>
+      <c r="S19">
+        <v>3.5</v>
+      </c>
+      <c r="T19">
+        <v>2.38</v>
+      </c>
+      <c r="U19">
+        <v>1.53</v>
+      </c>
+      <c r="V19">
+        <v>5.5</v>
+      </c>
+      <c r="W19">
+        <v>1.14</v>
+      </c>
+      <c r="X19">
+        <v>1.02</v>
+      </c>
+      <c r="Y19">
+        <v>14.4</v>
+      </c>
+      <c r="Z19">
+        <v>1.12</v>
+      </c>
+      <c r="AA19">
+        <v>4.8</v>
+      </c>
+      <c r="AB19">
+        <v>1.53</v>
+      </c>
+      <c r="AC19">
         <v>2.25</v>
       </c>
-      <c r="R19">
-        <v>1.5</v>
-      </c>
-      <c r="S19">
-        <v>2.5</v>
-      </c>
-      <c r="T19">
-        <v>3.5</v>
-      </c>
-      <c r="U19">
-        <v>1.29</v>
-      </c>
-      <c r="V19">
-        <v>10</v>
-      </c>
-      <c r="W19">
-        <v>1.06</v>
-      </c>
-      <c r="X19">
-        <v>1.09</v>
-      </c>
-      <c r="Y19">
-        <v>7</v>
-      </c>
-      <c r="Z19">
-        <v>1.44</v>
-      </c>
-      <c r="AA19">
-        <v>2.7</v>
-      </c>
-      <c r="AB19">
-        <v>2.3</v>
-      </c>
-      <c r="AC19">
-        <v>1.62</v>
-      </c>
       <c r="AD19">
-        <v>4.33</v>
+        <v>2.42</v>
       </c>
       <c r="AE19">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="AF19">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="AG19">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AH19">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="AI19">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="AJ19" t="s">
-        <v>176</v>
+        <v>159</v>
       </c>
       <c r="AK19" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL19">
-        <v>1.4</v>
-      </c>
-      <c r="AM19">
-        <v>1.3</v>
-      </c>
-      <c r="AN19">
-        <v>1.5</v>
-      </c>
-      <c r="AO19">
-        <v>8</v>
-      </c>
-      <c r="AP19">
-        <v>1.3</v>
-      </c>
-      <c r="AQ19">
-        <v>1.58</v>
-      </c>
-      <c r="AR19">
-        <v>2</v>
-      </c>
-      <c r="AS19">
-        <v>2.64</v>
-      </c>
-      <c r="AT19">
-        <v>3.58</v>
-      </c>
-      <c r="AU19">
-        <v>2.97</v>
-      </c>
-      <c r="AV19">
-        <v>2.17</v>
-      </c>
-      <c r="AW19">
-        <v>1.73</v>
-      </c>
-      <c r="AX19">
-        <v>1.4</v>
-      </c>
-      <c r="AY19">
-        <v>1.21</v>
-      </c>
-      <c r="AZ19">
-        <v>0</v>
-      </c>
-      <c r="BA19">
-        <v>0</v>
-      </c>
-      <c r="BB19">
-        <v>1.83</v>
-      </c>
-      <c r="BC19">
-        <v>2.25</v>
-      </c>
-      <c r="BD19" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL19" s="3">
         <v>45771.58333333334</v>
       </c>
     </row>
-    <row r="20" spans="1:56">
+    <row r="20" spans="1:38">
       <c r="A20" s="2">
         <v>45771</v>
       </c>
       <c r="B20" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C20" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="D20" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="F20" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="G20">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J20">
         <v>1</v>
       </c>
       <c r="K20" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L20">
-        <v>3.07</v>
+        <v>1.9</v>
       </c>
       <c r="M20">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N20">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="O20">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="P20">
-        <v>10</v>
+        <v>8.5</v>
       </c>
       <c r="Q20">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="R20">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S20">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T20">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="U20">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V20">
-        <v>5.15</v>
+        <v>7.8</v>
       </c>
       <c r="W20">
-        <v>1.1</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="Y20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AA20">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AB20">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AC20">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AD20">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AE20">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AF20">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="AG20">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AH20">
-        <v>4.2</v>
+        <v>7</v>
       </c>
       <c r="AI20">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="AJ20" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="AK20" t="s">
-        <v>202</v>
-      </c>
-      <c r="AL20">
-        <v>1.65</v>
-      </c>
-      <c r="AM20">
-        <v>1.25</v>
-      </c>
-      <c r="AN20">
-        <v>1.36</v>
-      </c>
-      <c r="AO20">
-        <v>10</v>
-      </c>
-      <c r="AP20">
-        <v>0</v>
-      </c>
-      <c r="AQ20">
-        <v>0</v>
-      </c>
-      <c r="AR20">
-        <v>0</v>
-      </c>
-      <c r="AS20">
-        <v>0</v>
-      </c>
-      <c r="AT20">
-        <v>0</v>
-      </c>
-      <c r="AU20">
-        <v>0</v>
-      </c>
-      <c r="AV20">
-        <v>0</v>
-      </c>
-      <c r="AW20">
-        <v>0</v>
-      </c>
-      <c r="AX20">
-        <v>0</v>
-      </c>
-      <c r="AY20">
-        <v>0</v>
-      </c>
-      <c r="AZ20">
-        <v>0</v>
-      </c>
-      <c r="BA20">
-        <v>0</v>
-      </c>
-      <c r="BB20">
-        <v>2.15</v>
-      </c>
-      <c r="BC20">
-        <v>1.83</v>
-      </c>
-      <c r="BD20" s="3">
+        <v>186</v>
+      </c>
+      <c r="AL20" s="3">
         <v>45771.625</v>
       </c>
     </row>
-    <row r="21" spans="1:56">
+    <row r="21" spans="1:38">
       <c r="A21" s="2">
         <v>45771</v>
       </c>
       <c r="B21" t="s">
-        <v>62</v>
+        <v>44</v>
       </c>
       <c r="C21" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="D21" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E21" t="s">
-        <v>111</v>
+        <v>95</v>
       </c>
       <c r="F21" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="K21" t="s">
         <v>146</v>
       </c>
-      <c r="G21">
-        <v>4</v>
-      </c>
-      <c r="H21">
-        <v>3</v>
-      </c>
-      <c r="I21">
-        <v>3</v>
-      </c>
-      <c r="J21">
-        <v>1</v>
-      </c>
-      <c r="K21" t="s">
-        <v>162</v>
-      </c>
       <c r="L21">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="M21">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N21">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="O21">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="P21">
-        <v>8.5</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="R21">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="S21">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="T21">
-        <v>2.91</v>
+        <v>2.3</v>
       </c>
       <c r="U21">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="V21">
-        <v>7.8</v>
+        <v>5.15</v>
       </c>
       <c r="W21">
-        <v>1.02</v>
+        <v>1.1</v>
       </c>
       <c r="X21">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Z21">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AA21">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
       <c r="AB21">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AC21">
-        <v>1.75</v>
+        <v>2.2</v>
       </c>
       <c r="AD21">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AE21">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AF21">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AG21">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AH21">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="AI21">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="AJ21" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="AK21" t="s">
-        <v>203</v>
-      </c>
-      <c r="AL21">
-        <v>1.22</v>
-      </c>
-      <c r="AM21">
-        <v>1.25</v>
-      </c>
-      <c r="AN21">
-        <v>1.83</v>
-      </c>
-      <c r="AO21">
-        <v>16</v>
-      </c>
-      <c r="AP21">
-        <v>1.27</v>
-      </c>
-      <c r="AQ21">
-        <v>1.51</v>
-      </c>
-      <c r="AR21">
-        <v>1.89</v>
-      </c>
-      <c r="AS21">
-        <v>2.46</v>
-      </c>
-      <c r="AT21">
-        <v>3.34</v>
-      </c>
-      <c r="AU21">
-        <v>3.14</v>
-      </c>
-      <c r="AV21">
-        <v>2.26</v>
-      </c>
-      <c r="AW21">
-        <v>1.77</v>
-      </c>
-      <c r="AX21">
-        <v>1.43</v>
-      </c>
-      <c r="AY21">
-        <v>1.24</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>1.57</v>
-      </c>
-      <c r="BC21">
-        <v>2.63</v>
-      </c>
-      <c r="BD21" s="3">
+        <v>187</v>
+      </c>
+      <c r="AL21" s="3">
         <v>45771.625</v>
       </c>
     </row>
-    <row r="22" spans="1:56">
+    <row r="22" spans="1:38">
       <c r="A22" s="2">
         <v>45771</v>
       </c>
       <c r="B22" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C22" t="s">
-        <v>84</v>
+        <v>67</v>
       </c>
       <c r="D22" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E22" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="F22" t="s">
-        <v>147</v>
+        <v>131</v>
       </c>
       <c r="G22">
         <v>2</v>
@@ -4618,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="K22" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L22">
         <v>4</v>
@@ -4693,427 +3514,265 @@
         <v>0</v>
       </c>
       <c r="AJ22" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="AK22" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL22">
-        <v>0</v>
-      </c>
-      <c r="AM22">
-        <v>0</v>
-      </c>
-      <c r="AN22">
-        <v>0</v>
-      </c>
-      <c r="AO22">
-        <v>7</v>
-      </c>
-      <c r="AP22">
-        <v>0</v>
-      </c>
-      <c r="AQ22">
-        <v>0</v>
-      </c>
-      <c r="AR22">
-        <v>0</v>
-      </c>
-      <c r="AS22">
-        <v>0</v>
-      </c>
-      <c r="AT22">
-        <v>0</v>
-      </c>
-      <c r="AU22">
-        <v>0</v>
-      </c>
-      <c r="AV22">
-        <v>0</v>
-      </c>
-      <c r="AW22">
-        <v>0</v>
-      </c>
-      <c r="AX22">
-        <v>0</v>
-      </c>
-      <c r="AY22">
-        <v>0</v>
-      </c>
-      <c r="AZ22">
-        <v>0</v>
-      </c>
-      <c r="BA22">
-        <v>0</v>
-      </c>
-      <c r="BB22">
-        <v>2.6</v>
-      </c>
-      <c r="BC22">
-        <v>1.57</v>
-      </c>
-      <c r="BD22" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL22" s="3">
         <v>45771.64583333334</v>
       </c>
     </row>
-    <row r="23" spans="1:56">
+    <row r="23" spans="1:38">
       <c r="A23" s="2">
         <v>45771</v>
       </c>
       <c r="B23" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C23" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="D23" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="F23" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I23">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23">
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L23">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="M23">
-        <v>3.2</v>
+        <v>3.63</v>
       </c>
       <c r="N23">
-        <v>3.1</v>
+        <v>3.87</v>
       </c>
       <c r="O23">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Q23">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="R23">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S23">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T23">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U23">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V23">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="W23">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y23">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="Z23">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AA23">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AB23">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AC23">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AD23">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AE23">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AF23">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AG23">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH23">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="AI23">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AJ23" t="s">
-        <v>180</v>
+        <v>147</v>
       </c>
       <c r="AK23" t="s">
-        <v>204</v>
-      </c>
-      <c r="AL23">
-        <v>0</v>
-      </c>
-      <c r="AM23">
-        <v>0</v>
-      </c>
-      <c r="AN23">
-        <v>0</v>
-      </c>
-      <c r="AO23">
-        <v>10</v>
-      </c>
-      <c r="AP23">
-        <v>0</v>
-      </c>
-      <c r="AQ23">
-        <v>0</v>
-      </c>
-      <c r="AR23">
-        <v>0</v>
-      </c>
-      <c r="AS23">
-        <v>0</v>
-      </c>
-      <c r="AT23">
-        <v>0</v>
-      </c>
-      <c r="AU23">
-        <v>0</v>
-      </c>
-      <c r="AV23">
-        <v>0</v>
-      </c>
-      <c r="AW23">
-        <v>0</v>
-      </c>
-      <c r="AX23">
-        <v>0</v>
-      </c>
-      <c r="AY23">
-        <v>0</v>
-      </c>
-      <c r="AZ23">
-        <v>0</v>
-      </c>
-      <c r="BA23">
-        <v>0</v>
-      </c>
-      <c r="BB23">
-        <v>1.73</v>
-      </c>
-      <c r="BC23">
-        <v>2.3</v>
-      </c>
-      <c r="BD23" s="3">
+        <v>188</v>
+      </c>
+      <c r="AL23" s="3">
         <v>45771.64583333334</v>
       </c>
     </row>
-    <row r="24" spans="1:56">
+    <row r="24" spans="1:38">
       <c r="A24" s="2">
         <v>45771</v>
       </c>
       <c r="B24" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
       <c r="C24" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="D24" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="F24" t="s">
-        <v>149</v>
+        <v>133</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J24">
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L24">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M24">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="N24">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O24">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="P24">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Q24">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="R24">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S24">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T24">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U24">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V24">
-        <v>6.25</v>
+        <v>8</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X24">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y24">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="Z24">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AA24">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AB24">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AC24">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AD24">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AE24">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AF24">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AG24">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH24">
-        <v>5.68</v>
+        <v>0</v>
       </c>
       <c r="AI24">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AK24" t="s">
-        <v>205</v>
-      </c>
-      <c r="AL24">
-        <v>1.25</v>
-      </c>
-      <c r="AM24">
-        <v>1.22</v>
-      </c>
-      <c r="AN24">
-        <v>1.85</v>
-      </c>
-      <c r="AO24">
-        <v>4</v>
-      </c>
-      <c r="AP24">
-        <v>1.33</v>
-      </c>
-      <c r="AQ24">
-        <v>1.56</v>
-      </c>
-      <c r="AR24">
-        <v>1.93</v>
-      </c>
-      <c r="AS24">
-        <v>2.43</v>
-      </c>
-      <c r="AT24">
-        <v>3.15</v>
-      </c>
-      <c r="AU24">
-        <v>2.95</v>
-      </c>
-      <c r="AV24">
-        <v>2.23</v>
-      </c>
-      <c r="AW24">
-        <v>1.77</v>
-      </c>
-      <c r="AX24">
-        <v>1.48</v>
-      </c>
-      <c r="AY24">
-        <v>1.29</v>
-      </c>
-      <c r="AZ24">
-        <v>0</v>
-      </c>
-      <c r="BA24">
-        <v>0</v>
-      </c>
-      <c r="BB24">
-        <v>1.67</v>
-      </c>
-      <c r="BC24">
-        <v>2.5</v>
-      </c>
-      <c r="BD24" s="3">
+        <v>189</v>
+      </c>
+      <c r="AL24" s="3">
         <v>45771.64583333334</v>
       </c>
     </row>
-    <row r="25" spans="1:56">
+    <row r="25" spans="1:38">
       <c r="A25" s="2">
         <v>45771</v>
       </c>
       <c r="B25" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="F25" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -5128,7 +3787,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L25">
         <v>4.2</v>
@@ -5203,87 +3862,33 @@
         <v>0</v>
       </c>
       <c r="AJ25" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK25" t="s">
-        <v>197</v>
-      </c>
-      <c r="AL25">
-        <v>1.95</v>
-      </c>
-      <c r="AM25">
-        <v>1.2</v>
-      </c>
-      <c r="AN25">
-        <v>1.17</v>
-      </c>
-      <c r="AO25">
-        <v>-1</v>
-      </c>
-      <c r="AP25">
-        <v>0</v>
-      </c>
-      <c r="AQ25">
-        <v>0</v>
-      </c>
-      <c r="AR25">
-        <v>0</v>
-      </c>
-      <c r="AS25">
-        <v>0</v>
-      </c>
-      <c r="AT25">
-        <v>0</v>
-      </c>
-      <c r="AU25">
-        <v>0</v>
-      </c>
-      <c r="AV25">
-        <v>0</v>
-      </c>
-      <c r="AW25">
-        <v>0</v>
-      </c>
-      <c r="AX25">
-        <v>0</v>
-      </c>
-      <c r="AY25">
-        <v>0</v>
-      </c>
-      <c r="AZ25">
-        <v>0</v>
-      </c>
-      <c r="BA25">
-        <v>0</v>
-      </c>
-      <c r="BB25">
-        <v>2.75</v>
-      </c>
-      <c r="BC25">
-        <v>1.57</v>
-      </c>
-      <c r="BD25" s="3">
+        <v>181</v>
+      </c>
+      <c r="AL25" s="3">
         <v>45771.65625</v>
       </c>
     </row>
-    <row r="26" spans="1:56">
+    <row r="26" spans="1:38">
       <c r="A26" s="2">
         <v>45771</v>
       </c>
       <c r="B26" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C26" t="s">
-        <v>79</v>
+        <v>62</v>
       </c>
       <c r="D26" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E26" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="F26" t="s">
-        <v>151</v>
+        <v>135</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -5298,7 +3903,7 @@
         <v>1</v>
       </c>
       <c r="K26" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L26">
         <v>4.1</v>
@@ -5373,87 +3978,33 @@
         <v>1.25</v>
       </c>
       <c r="AJ26" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="AK26" t="s">
-        <v>206</v>
-      </c>
-      <c r="AL26">
-        <v>1.93</v>
-      </c>
-      <c r="AM26">
-        <v>1.2</v>
-      </c>
-      <c r="AN26">
-        <v>1.25</v>
-      </c>
-      <c r="AO26">
-        <v>8</v>
-      </c>
-      <c r="AP26">
-        <v>1.21</v>
-      </c>
-      <c r="AQ26">
-        <v>1.42</v>
-      </c>
-      <c r="AR26">
-        <v>1.8</v>
-      </c>
-      <c r="AS26">
-        <v>2.21</v>
-      </c>
-      <c r="AT26">
-        <v>2.92</v>
-      </c>
-      <c r="AU26">
-        <v>3.58</v>
-      </c>
-      <c r="AV26">
-        <v>2.57</v>
-      </c>
-      <c r="AW26">
-        <v>1.91</v>
-      </c>
-      <c r="AX26">
-        <v>1.56</v>
-      </c>
-      <c r="AY26">
-        <v>1.31</v>
-      </c>
-      <c r="AZ26">
-        <v>0</v>
-      </c>
-      <c r="BA26">
-        <v>0</v>
-      </c>
-      <c r="BB26">
-        <v>2.5</v>
-      </c>
-      <c r="BC26">
-        <v>1.5</v>
-      </c>
-      <c r="BD26" s="3">
+        <v>190</v>
+      </c>
+      <c r="AL26" s="3">
         <v>45771.66666666666</v>
       </c>
     </row>
-    <row r="27" spans="1:56">
+    <row r="27" spans="1:38">
       <c r="A27" s="2">
         <v>45771</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="D27" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E27" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="F27" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="G27">
         <v>1</v>
@@ -5468,7 +4019,7 @@
         <v>0</v>
       </c>
       <c r="K27" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L27">
         <v>4.75</v>
@@ -5543,800 +4094,530 @@
         <v>1.25</v>
       </c>
       <c r="AJ27" t="s">
-        <v>182</v>
+        <v>165</v>
       </c>
       <c r="AK27" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL27">
-        <v>2.38</v>
-      </c>
-      <c r="AM27">
-        <v>0</v>
-      </c>
-      <c r="AN27">
-        <v>1.17</v>
-      </c>
-      <c r="AO27">
-        <v>9</v>
-      </c>
-      <c r="AP27">
-        <v>1.15</v>
-      </c>
-      <c r="AQ27">
-        <v>1.22</v>
-      </c>
-      <c r="AR27">
-        <v>1.42</v>
-      </c>
-      <c r="AS27">
-        <v>1.77</v>
-      </c>
-      <c r="AT27">
-        <v>2.2</v>
-      </c>
-      <c r="AU27">
-        <v>4.75</v>
-      </c>
-      <c r="AV27">
-        <v>3.5</v>
-      </c>
-      <c r="AW27">
-        <v>2.57</v>
-      </c>
-      <c r="AX27">
-        <v>1.98</v>
-      </c>
-      <c r="AY27">
-        <v>1.62</v>
-      </c>
-      <c r="AZ27">
-        <v>0</v>
-      </c>
-      <c r="BA27">
-        <v>0</v>
-      </c>
-      <c r="BB27">
-        <v>3.4</v>
-      </c>
-      <c r="BC27">
-        <v>1.3</v>
-      </c>
-      <c r="BD27" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL27" s="3">
         <v>45771.67708333334</v>
       </c>
     </row>
-    <row r="28" spans="1:56">
+    <row r="28" spans="1:38">
       <c r="A28" s="2">
         <v>45771</v>
       </c>
       <c r="B28" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C28" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E28" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>153</v>
+        <v>137</v>
       </c>
       <c r="G28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L28">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="M28">
-        <v>5.75</v>
+        <v>3.91</v>
       </c>
       <c r="N28">
-        <v>13</v>
+        <v>5.68</v>
       </c>
       <c r="O28">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="P28">
-        <v>23</v>
+        <v>8.5</v>
       </c>
       <c r="Q28">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="R28">
+        <v>1.44</v>
+      </c>
+      <c r="S28">
+        <v>2.63</v>
+      </c>
+      <c r="T28">
+        <v>3.25</v>
+      </c>
+      <c r="U28">
+        <v>1.33</v>
+      </c>
+      <c r="V28">
+        <v>9</v>
+      </c>
+      <c r="W28">
+        <v>1.07</v>
+      </c>
+      <c r="X28">
+        <v>1.06</v>
+      </c>
+      <c r="Y28">
+        <v>8.5</v>
+      </c>
+      <c r="Z28">
+        <v>1.35</v>
+      </c>
+      <c r="AA28">
+        <v>3.1</v>
+      </c>
+      <c r="AB28">
+        <v>2</v>
+      </c>
+      <c r="AC28">
+        <v>1.72</v>
+      </c>
+      <c r="AD28">
+        <v>3.7</v>
+      </c>
+      <c r="AE28">
         <v>1.25</v>
       </c>
-      <c r="S28">
-        <v>3.75</v>
-      </c>
-      <c r="T28">
-        <v>2.2</v>
-      </c>
-      <c r="U28">
-        <v>1.62</v>
-      </c>
-      <c r="V28">
-        <v>5</v>
-      </c>
-      <c r="W28">
-        <v>1.17</v>
-      </c>
-      <c r="X28">
-        <v>1.01</v>
-      </c>
-      <c r="Y28">
-        <v>17</v>
-      </c>
-      <c r="Z28">
-        <v>1.15</v>
-      </c>
-      <c r="AA28">
-        <v>5.25</v>
-      </c>
-      <c r="AB28">
-        <v>1.5</v>
-      </c>
-      <c r="AC28">
-        <v>2.63</v>
-      </c>
-      <c r="AD28">
-        <v>2.2</v>
-      </c>
-      <c r="AE28">
-        <v>1.6</v>
-      </c>
       <c r="AF28">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AG28">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH28">
-        <v>3.9</v>
+        <v>7.5</v>
       </c>
       <c r="AI28">
-        <v>1.25</v>
+        <v>1.08</v>
       </c>
       <c r="AJ28" t="s">
-        <v>183</v>
+        <v>166</v>
       </c>
       <c r="AK28" t="s">
-        <v>194</v>
-      </c>
-      <c r="AL28">
-        <v>1.04</v>
-      </c>
-      <c r="AM28">
-        <v>1.11</v>
-      </c>
-      <c r="AN28">
-        <v>4</v>
-      </c>
-      <c r="AO28">
-        <v>8</v>
-      </c>
-      <c r="AP28">
-        <v>1.33</v>
-      </c>
-      <c r="AQ28">
-        <v>1.7</v>
-      </c>
-      <c r="AR28">
-        <v>2.04</v>
-      </c>
-      <c r="AS28">
-        <v>2.66</v>
-      </c>
-      <c r="AT28">
-        <v>3.7</v>
-      </c>
-      <c r="AU28">
-        <v>2.93</v>
-      </c>
-      <c r="AV28">
-        <v>2.05</v>
-      </c>
-      <c r="AW28">
-        <v>1.66</v>
-      </c>
-      <c r="AX28">
-        <v>1.37</v>
-      </c>
-      <c r="AY28">
-        <v>1.2</v>
-      </c>
-      <c r="AZ28">
-        <v>0</v>
-      </c>
-      <c r="BA28">
-        <v>0</v>
-      </c>
-      <c r="BB28">
-        <v>1.18</v>
-      </c>
-      <c r="BC28">
-        <v>5</v>
-      </c>
-      <c r="BD28" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL28" s="3">
         <v>45771.6875</v>
       </c>
     </row>
-    <row r="29" spans="1:56">
+    <row r="29" spans="1:38">
       <c r="A29" s="2">
         <v>45771</v>
       </c>
       <c r="B29" t="s">
-        <v>67</v>
+        <v>49</v>
       </c>
       <c r="C29" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="D29" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="E29" t="s">
-        <v>119</v>
+        <v>103</v>
       </c>
       <c r="F29" t="s">
-        <v>154</v>
+        <v>138</v>
       </c>
       <c r="G29">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
+        <v>1</v>
+      </c>
+      <c r="J29">
+        <v>1</v>
+      </c>
+      <c r="K29" t="s">
+        <v>146</v>
+      </c>
+      <c r="L29">
+        <v>1.22</v>
+      </c>
+      <c r="M29">
+        <v>5.75</v>
+      </c>
+      <c r="N29">
+        <v>13</v>
+      </c>
+      <c r="O29">
+        <v>1.18</v>
+      </c>
+      <c r="P29">
+        <v>23</v>
+      </c>
+      <c r="Q29">
+        <v>5</v>
+      </c>
+      <c r="R29">
+        <v>1.25</v>
+      </c>
+      <c r="S29">
+        <v>3.75</v>
+      </c>
+      <c r="T29">
+        <v>2.2</v>
+      </c>
+      <c r="U29">
+        <v>1.62</v>
+      </c>
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29">
+        <v>1.17</v>
+      </c>
+      <c r="X29">
+        <v>1.01</v>
+      </c>
+      <c r="Y29">
+        <v>17</v>
+      </c>
+      <c r="Z29">
+        <v>1.15</v>
+      </c>
+      <c r="AA29">
+        <v>5.25</v>
+      </c>
+      <c r="AB29">
+        <v>1.5</v>
+      </c>
+      <c r="AC29">
+        <v>2.63</v>
+      </c>
+      <c r="AD29">
+        <v>2.2</v>
+      </c>
+      <c r="AE29">
+        <v>1.6</v>
+      </c>
+      <c r="AF29">
         <v>2</v>
       </c>
-      <c r="J29">
-        <v>0</v>
-      </c>
-      <c r="K29" t="s">
-        <v>162</v>
-      </c>
-      <c r="L29">
-        <v>1.65</v>
-      </c>
-      <c r="M29">
-        <v>3.91</v>
-      </c>
-      <c r="N29">
-        <v>5.68</v>
-      </c>
-      <c r="O29">
-        <v>1.4</v>
-      </c>
-      <c r="P29">
-        <v>8.5</v>
-      </c>
-      <c r="Q29">
-        <v>3.4</v>
-      </c>
-      <c r="R29">
-        <v>1.44</v>
-      </c>
-      <c r="S29">
-        <v>2.63</v>
-      </c>
-      <c r="T29">
-        <v>3.25</v>
-      </c>
-      <c r="U29">
-        <v>1.33</v>
-      </c>
-      <c r="V29">
-        <v>9</v>
-      </c>
-      <c r="W29">
-        <v>1.07</v>
-      </c>
-      <c r="X29">
-        <v>1.06</v>
-      </c>
-      <c r="Y29">
-        <v>8.5</v>
-      </c>
-      <c r="Z29">
-        <v>1.35</v>
-      </c>
-      <c r="AA29">
-        <v>3.1</v>
-      </c>
-      <c r="AB29">
-        <v>2</v>
-      </c>
-      <c r="AC29">
-        <v>1.72</v>
-      </c>
-      <c r="AD29">
-        <v>3.7</v>
-      </c>
-      <c r="AE29">
+      <c r="AG29">
+        <v>1.75</v>
+      </c>
+      <c r="AH29">
+        <v>3.9</v>
+      </c>
+      <c r="AI29">
         <v>1.25</v>
       </c>
-      <c r="AF29">
-        <v>2.1</v>
-      </c>
-      <c r="AG29">
-        <v>1.67</v>
-      </c>
-      <c r="AH29">
-        <v>7.5</v>
-      </c>
-      <c r="AI29">
-        <v>1.08</v>
-      </c>
       <c r="AJ29" t="s">
-        <v>184</v>
+        <v>167</v>
       </c>
       <c r="AK29" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL29">
-        <v>1.13</v>
-      </c>
-      <c r="AM29">
-        <v>1.2</v>
-      </c>
-      <c r="AN29">
-        <v>2.3</v>
-      </c>
-      <c r="AO29">
-        <v>9</v>
-      </c>
-      <c r="AP29">
-        <v>1.26</v>
-      </c>
-      <c r="AQ29">
-        <v>1.51</v>
-      </c>
-      <c r="AR29">
-        <v>1.85</v>
-      </c>
-      <c r="AS29">
-        <v>2.45</v>
-      </c>
-      <c r="AT29">
-        <v>3.28</v>
-      </c>
-      <c r="AU29">
-        <v>3.22</v>
-      </c>
-      <c r="AV29">
-        <v>2.32</v>
-      </c>
-      <c r="AW29">
-        <v>1.85</v>
-      </c>
-      <c r="AX29">
-        <v>1.46</v>
-      </c>
-      <c r="AY29">
-        <v>1.25</v>
-      </c>
-      <c r="AZ29">
-        <v>0</v>
-      </c>
-      <c r="BA29">
-        <v>0</v>
-      </c>
-      <c r="BB29">
-        <v>1.4</v>
-      </c>
-      <c r="BC29">
-        <v>3.4</v>
-      </c>
-      <c r="BD29" s="3">
+        <v>177</v>
+      </c>
+      <c r="AL29" s="3">
         <v>45771.6875</v>
       </c>
     </row>
-    <row r="30" spans="1:56">
+    <row r="30" spans="1:38">
       <c r="A30" s="2">
         <v>45771</v>
       </c>
       <c r="B30" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="C30" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="D30" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="F30" t="s">
-        <v>155</v>
+        <v>139</v>
       </c>
       <c r="G30">
         <v>2</v>
       </c>
       <c r="H30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J30">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K30" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L30">
-        <v>1.94</v>
+        <v>3.42</v>
       </c>
       <c r="M30">
-        <v>3.32</v>
+        <v>2.73</v>
       </c>
       <c r="N30">
-        <v>3.93</v>
+        <v>2.34</v>
       </c>
       <c r="O30">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="P30">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="Q30">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R30">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T30">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U30">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V30">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W30">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X30">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y30">
-        <v>8.699999999999999</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AA30">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="AB30">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="AC30">
-        <v>1.79</v>
+        <v>1.55</v>
       </c>
       <c r="AD30">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="AE30">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AF30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG30">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH30">
-        <v>6.45</v>
+        <v>0</v>
       </c>
       <c r="AI30">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="s">
-        <v>185</v>
+        <v>168</v>
       </c>
       <c r="AK30" t="s">
-        <v>207</v>
-      </c>
-      <c r="AL30">
-        <v>1.25</v>
-      </c>
-      <c r="AM30">
-        <v>1.25</v>
-      </c>
-      <c r="AN30">
-        <v>1.83</v>
-      </c>
-      <c r="AO30">
-        <v>15</v>
-      </c>
-      <c r="AP30">
-        <v>1.11</v>
-      </c>
-      <c r="AQ30">
-        <v>1.21</v>
-      </c>
-      <c r="AR30">
-        <v>1.36</v>
-      </c>
-      <c r="AS30">
-        <v>1.57</v>
-      </c>
-      <c r="AT30">
-        <v>1.88</v>
-      </c>
-      <c r="AU30">
-        <v>5.3</v>
-      </c>
-      <c r="AV30">
-        <v>3.8</v>
-      </c>
-      <c r="AW30">
-        <v>2.8</v>
-      </c>
-      <c r="AX30">
-        <v>2.23</v>
-      </c>
-      <c r="AY30">
-        <v>1.81</v>
-      </c>
-      <c r="AZ30">
-        <v>0</v>
-      </c>
-      <c r="BA30">
-        <v>0</v>
-      </c>
-      <c r="BB30">
-        <v>1.57</v>
-      </c>
-      <c r="BC30">
-        <v>2.75</v>
-      </c>
-      <c r="BD30" s="3">
-        <v>45771.79166666666</v>
+        <v>191</v>
+      </c>
+      <c r="AL30" s="3">
+        <v>45771.75</v>
       </c>
     </row>
-    <row r="31" spans="1:56">
+    <row r="31" spans="1:38">
       <c r="A31" s="2">
         <v>45771</v>
       </c>
       <c r="B31" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C31" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>105</v>
       </c>
       <c r="F31" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="G31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>163</v>
+        <v>146</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T31">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U31">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X31">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y31">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="Z31">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AA31">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AB31">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AC31">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD31">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AE31">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AF31">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG31">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH31">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AI31">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AJ31" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="AK31" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL31">
-        <v>0</v>
-      </c>
-      <c r="AM31">
-        <v>0</v>
-      </c>
-      <c r="AN31">
-        <v>0</v>
-      </c>
-      <c r="AO31">
-        <v>-1</v>
-      </c>
-      <c r="AP31">
-        <v>0</v>
-      </c>
-      <c r="AQ31">
-        <v>0</v>
-      </c>
-      <c r="AR31">
-        <v>0</v>
-      </c>
-      <c r="AS31">
-        <v>0</v>
-      </c>
-      <c r="AT31">
-        <v>0</v>
-      </c>
-      <c r="AU31">
-        <v>0</v>
-      </c>
-      <c r="AV31">
-        <v>0</v>
-      </c>
-      <c r="AW31">
-        <v>0</v>
-      </c>
-      <c r="AX31">
-        <v>0</v>
-      </c>
-      <c r="AY31">
-        <v>0</v>
-      </c>
-      <c r="AZ31">
-        <v>0</v>
-      </c>
-      <c r="BA31">
-        <v>0</v>
-      </c>
-      <c r="BB31">
-        <v>0</v>
-      </c>
-      <c r="BC31">
-        <v>0</v>
-      </c>
-      <c r="BD31" s="3">
+        <v>192</v>
+      </c>
+      <c r="AL31" s="3">
         <v>45771.79166666666</v>
       </c>
     </row>
-    <row r="32" spans="1:56">
+    <row r="32" spans="1:38">
       <c r="A32" s="2">
         <v>45771</v>
       </c>
       <c r="B32" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="C32" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E32" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="F32" t="s">
-        <v>157</v>
+        <v>141</v>
       </c>
       <c r="G32">
         <v>2</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
         <v>2</v>
       </c>
-      <c r="J32">
-        <v>1</v>
-      </c>
       <c r="K32" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L32">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="M32">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N32">
-        <v>9.4</v>
+        <v>3.93</v>
       </c>
       <c r="O32">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="P32">
-        <v>8.75</v>
+        <v>8.5</v>
       </c>
       <c r="Q32">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="R32">
         <v>1.44</v>
@@ -6345,10 +4626,10 @@
         <v>2.63</v>
       </c>
       <c r="T32">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U32">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V32">
         <v>9</v>
@@ -6357,123 +4638,69 @@
         <v>1.07</v>
       </c>
       <c r="X32">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y32">
-        <v>8.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="Z32">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AA32">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="AB32">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="AC32">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AD32">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="AE32">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AF32">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AG32">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AH32">
-        <v>8</v>
+        <v>6.45</v>
       </c>
       <c r="AI32">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="AJ32" t="s">
-        <v>186</v>
+        <v>170</v>
       </c>
       <c r="AK32" t="s">
-        <v>208</v>
-      </c>
-      <c r="AL32">
-        <v>1.07</v>
-      </c>
-      <c r="AM32">
-        <v>1.19</v>
-      </c>
-      <c r="AN32">
-        <v>3</v>
-      </c>
-      <c r="AO32">
-        <v>5</v>
-      </c>
-      <c r="AP32">
-        <v>1.7</v>
-      </c>
-      <c r="AQ32">
-        <v>2.05</v>
-      </c>
-      <c r="AR32">
-        <v>2.92</v>
-      </c>
-      <c r="AS32">
-        <v>3.3</v>
-      </c>
-      <c r="AT32">
-        <v>4.4</v>
-      </c>
-      <c r="AU32">
-        <v>2.05</v>
-      </c>
-      <c r="AV32">
-        <v>1.7</v>
-      </c>
-      <c r="AW32">
-        <v>1.31</v>
-      </c>
-      <c r="AX32">
-        <v>1.28</v>
-      </c>
-      <c r="AY32">
-        <v>1.15</v>
-      </c>
-      <c r="AZ32">
-        <v>0</v>
-      </c>
-      <c r="BA32">
-        <v>0</v>
-      </c>
-      <c r="BB32">
-        <v>1.25</v>
-      </c>
-      <c r="BC32">
-        <v>5</v>
-      </c>
-      <c r="BD32" s="3">
+        <v>193</v>
+      </c>
+      <c r="AL32" s="3">
         <v>45771.79166666666</v>
       </c>
     </row>
-    <row r="33" spans="1:56">
+    <row r="33" spans="1:38">
       <c r="A33" s="2">
         <v>45771</v>
       </c>
       <c r="B33" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C33" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D33" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E33" t="s">
-        <v>123</v>
+        <v>107</v>
       </c>
       <c r="F33" t="s">
-        <v>158</v>
+        <v>142</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -6488,7 +4715,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L33">
         <v>1.73</v>
@@ -6563,87 +4790,33 @@
         <v>1.04</v>
       </c>
       <c r="AJ33" t="s">
-        <v>187</v>
+        <v>171</v>
       </c>
       <c r="AK33" t="s">
-        <v>164</v>
-      </c>
-      <c r="AL33">
-        <v>1.2</v>
-      </c>
-      <c r="AM33">
-        <v>1.22</v>
-      </c>
-      <c r="AN33">
-        <v>1.95</v>
-      </c>
-      <c r="AO33">
-        <v>10</v>
-      </c>
-      <c r="AP33">
-        <v>1.27</v>
-      </c>
-      <c r="AQ33">
-        <v>1.52</v>
-      </c>
-      <c r="AR33">
-        <v>1.85</v>
-      </c>
-      <c r="AS33">
-        <v>2.45</v>
-      </c>
-      <c r="AT33">
-        <v>3.28</v>
-      </c>
-      <c r="AU33">
-        <v>3.14</v>
-      </c>
-      <c r="AV33">
-        <v>2.3</v>
-      </c>
-      <c r="AW33">
-        <v>1.85</v>
-      </c>
-      <c r="AX33">
-        <v>1.46</v>
-      </c>
-      <c r="AY33">
-        <v>1.25</v>
-      </c>
-      <c r="AZ33">
-        <v>0</v>
-      </c>
-      <c r="BA33">
-        <v>0</v>
-      </c>
-      <c r="BB33">
-        <v>1.5</v>
-      </c>
-      <c r="BC33">
-        <v>3</v>
-      </c>
-      <c r="BD33" s="3">
+        <v>147</v>
+      </c>
+      <c r="AL33" s="3">
         <v>45771.875</v>
       </c>
     </row>
-    <row r="34" spans="1:56">
+    <row r="34" spans="1:38">
       <c r="A34" s="2">
         <v>45771</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>52</v>
       </c>
       <c r="C34" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D34" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E34" t="s">
-        <v>124</v>
+        <v>108</v>
       </c>
       <c r="F34" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -6658,7 +4831,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L34">
         <v>2.52</v>
@@ -6733,87 +4906,33 @@
         <v>1.3</v>
       </c>
       <c r="AJ34" t="s">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="AK34" t="s">
-        <v>209</v>
-      </c>
-      <c r="AL34">
-        <v>1.25</v>
-      </c>
-      <c r="AM34">
-        <v>0</v>
-      </c>
-      <c r="AN34">
-        <v>1.48</v>
-      </c>
-      <c r="AO34">
-        <v>9</v>
-      </c>
-      <c r="AP34">
-        <v>0</v>
-      </c>
-      <c r="AQ34">
-        <v>0</v>
-      </c>
-      <c r="AR34">
-        <v>0</v>
-      </c>
-      <c r="AS34">
-        <v>0</v>
-      </c>
-      <c r="AT34">
-        <v>0</v>
-      </c>
-      <c r="AU34">
-        <v>0</v>
-      </c>
-      <c r="AV34">
-        <v>0</v>
-      </c>
-      <c r="AW34">
-        <v>0</v>
-      </c>
-      <c r="AX34">
-        <v>0</v>
-      </c>
-      <c r="AY34">
-        <v>0</v>
-      </c>
-      <c r="AZ34">
-        <v>0</v>
-      </c>
-      <c r="BA34">
-        <v>0</v>
-      </c>
-      <c r="BB34">
-        <v>2.2</v>
-      </c>
-      <c r="BC34">
-        <v>1.62</v>
-      </c>
-      <c r="BD34" s="3">
+        <v>194</v>
+      </c>
+      <c r="AL34" s="3">
         <v>45771.875</v>
       </c>
     </row>
-    <row r="35" spans="1:56">
+    <row r="35" spans="1:38">
       <c r="A35" s="2">
         <v>45771</v>
       </c>
       <c r="B35" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="C35" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E35" t="s">
-        <v>125</v>
+        <v>109</v>
       </c>
       <c r="F35" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="G35">
         <v>2</v>
@@ -6828,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="K35" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L35">
         <v>1.82</v>
@@ -6903,87 +5022,33 @@
         <v>1.06</v>
       </c>
       <c r="AJ35" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="AK35" t="s">
-        <v>210</v>
-      </c>
-      <c r="AL35">
-        <v>1.18</v>
-      </c>
-      <c r="AM35">
-        <v>1.25</v>
-      </c>
-      <c r="AN35">
-        <v>2</v>
-      </c>
-      <c r="AO35">
-        <v>6</v>
-      </c>
-      <c r="AP35">
-        <v>1.3</v>
-      </c>
-      <c r="AQ35">
-        <v>1.57</v>
-      </c>
-      <c r="AR35">
-        <v>2.05</v>
-      </c>
-      <c r="AS35">
-        <v>2.6</v>
-      </c>
-      <c r="AT35">
-        <v>3.58</v>
-      </c>
-      <c r="AU35">
-        <v>2.97</v>
-      </c>
-      <c r="AV35">
-        <v>2.19</v>
-      </c>
-      <c r="AW35">
-        <v>1.7</v>
-      </c>
-      <c r="AX35">
-        <v>1.41</v>
-      </c>
-      <c r="AY35">
-        <v>1.21</v>
-      </c>
-      <c r="AZ35">
-        <v>0</v>
-      </c>
-      <c r="BA35">
-        <v>0</v>
-      </c>
-      <c r="BB35">
-        <v>1.5</v>
-      </c>
-      <c r="BC35">
-        <v>3.1</v>
-      </c>
-      <c r="BD35" s="3">
+        <v>195</v>
+      </c>
+      <c r="AL35" s="3">
         <v>45771.89583333334</v>
       </c>
     </row>
-    <row r="36" spans="1:56">
+    <row r="36" spans="1:38">
       <c r="A36" s="2">
         <v>45771</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>54</v>
       </c>
       <c r="C36" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>75</v>
       </c>
       <c r="E36" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="F36" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -6998,7 +5063,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="L36">
         <v>2.3</v>
@@ -7073,66 +5138,12 @@
         <v>1.03</v>
       </c>
       <c r="AJ36" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="AK36" t="s">
-        <v>211</v>
-      </c>
-      <c r="AL36">
-        <v>1.42</v>
-      </c>
-      <c r="AM36">
-        <v>1.33</v>
-      </c>
-      <c r="AN36">
-        <v>1.57</v>
-      </c>
-      <c r="AO36">
-        <v>13</v>
-      </c>
-      <c r="AP36">
-        <v>1.24</v>
-      </c>
-      <c r="AQ36">
-        <v>1.42</v>
-      </c>
-      <c r="AR36">
-        <v>1.73</v>
-      </c>
-      <c r="AS36">
-        <v>2.08</v>
-      </c>
-      <c r="AT36">
-        <v>2.62</v>
-      </c>
-      <c r="AU36">
-        <v>3.6</v>
-      </c>
-      <c r="AV36">
-        <v>2.67</v>
-      </c>
-      <c r="AW36">
-        <v>2.02</v>
-      </c>
-      <c r="AX36">
-        <v>1.65</v>
-      </c>
-      <c r="AY36">
-        <v>1.43</v>
-      </c>
-      <c r="AZ36">
-        <v>0</v>
-      </c>
-      <c r="BA36">
-        <v>0</v>
-      </c>
-      <c r="BB36">
-        <v>2.05</v>
-      </c>
-      <c r="BC36">
-        <v>2.05</v>
-      </c>
-      <c r="BD36" s="3">
+        <v>196</v>
+      </c>
+      <c r="AL36" s="3">
         <v>45771.89930555555</v>
       </c>
     </row>

--- a/jogos_2025-04-24.xlsx
+++ b/jogos_2025-04-24.xlsx
@@ -762,7 +762,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -772,22 +772,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Grobiņa</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>5.14</v>
+        <v>1.18</v>
       </c>
       <c r="M3" t="n">
-        <v>4.16</v>
+        <v>6</v>
       </c>
       <c r="N3" t="n">
+        <v>11</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>8</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y3" t="n">
         <v>1.48</v>
       </c>
-      <c r="O3" t="n">
-        <v>6</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="W3" t="n">
-        <v>0</v>
-      </c>
-      <c r="X3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z3" t="n">
-        <v>2.15</v>
+        <v>2.35</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
+          <t>['19', '87']</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>4</v>
+        <v>1.14</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>5.5</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45771.5</v>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,22 +1030,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grobiņa</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -1056,65 +1056,65 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>1.18</v>
+        <v>5.14</v>
       </c>
       <c r="M5" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="N5" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="O5" t="n">
         <v>6</v>
       </c>
-      <c r="N5" t="n">
-        <v>11</v>
-      </c>
-      <c r="O5" t="n">
-        <v>1.55</v>
-      </c>
       <c r="P5" t="n">
-        <v>2.95</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>8</v>
+        <v>1.91</v>
       </c>
       <c r="R5" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.02</v>
+        <v>2.22</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.48</v>
+        <v>1.67</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['19', '87']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -1123,16 +1123,16 @@
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>1.14</v>
+        <v>4</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5.5</v>
+        <v>1.29</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45771.5</v>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>ÍBV</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J8" t="n">
         <v>1</v>
@@ -1443,83 +1443,83 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>5.7</v>
+        <v>2.5</v>
       </c>
       <c r="M8" t="n">
-        <v>3.72</v>
+        <v>3.4</v>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>2.55</v>
       </c>
       <c r="O8" t="n">
-        <v>5.5</v>
+        <v>2.84</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.24</v>
       </c>
       <c r="S8" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T8" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="U8" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="V8" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="X8" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.87</v>
+        <v>1.57</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>['10', '24', '81']</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI8" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>['4', '9', '25', '28']</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>3.25</v>
-      </c>
       <c r="AJ8" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45771.54166666666</v>
@@ -1665,32 +1665,32 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>ÍBV</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H10" t="n">
         <v>1</v>
       </c>
       <c r="I10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>1</v>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.5</v>
+        <v>5.7</v>
       </c>
       <c r="M10" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="N10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X10" t="n">
         <v>3.4</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="O10" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="Y10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AA10" t="n">
         <v>3.1</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.48</v>
+        <v>1.91</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>['10', '24', '81']</t>
+          <t>['4', '9', '25', '28']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['41']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45771.54166666666</v>
@@ -2062,25 +2062,25 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>GAIS</t>
+          <t>Djurgården</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brommapojkarna</t>
+          <t>Öster</t>
         </is>
       </c>
       <c r="G13" t="n">
         <v>1</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -2088,83 +2088,83 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="M13" t="n">
-        <v>3.59</v>
+        <v>4.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.74</v>
+        <v>6.2</v>
       </c>
       <c r="O13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P13" t="n">
         <v>2.5</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>6</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z13" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q13" t="n">
-        <v>4</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X13" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AA13" t="n">
-        <v>2.78</v>
+        <v>2.42</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>['87']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.28</v>
+        <v>1.11</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.8</v>
+        <v>2.75</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.57</v>
+        <v>1.3</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,22 +2191,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.45</v>
+        <v>2.55</v>
       </c>
       <c r="M14" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O14" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="P14" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="n">
-        <v>4.45</v>
+        <v>3.6</v>
       </c>
       <c r="R14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="S14" t="n">
-        <v>2.04</v>
+        <v>2.5</v>
       </c>
       <c r="T14" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="U14" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.2</v>
       </c>
-      <c r="V14" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AC14" t="n">
-        <v>2.42</v>
+        <v>1.95</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
+          <t>['25']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AG14" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AH14" t="n">
         <v>1.5</v>
       </c>
       <c r="AI14" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2310,26 +2310,26 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
         <v>1</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N15" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O15" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Y15" t="n">
         <v>2.2</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O15" t="n">
-        <v>5</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Z15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['90+2']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['54']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AJ15" t="n">
         <v>2.2</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['-1', '-1']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['-1']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AJ15" t="n">
-        <v>1.44</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,22 +2449,22 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2475,65 +2475,65 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="N16" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="O16" t="n">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>4.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="S16" t="n">
-        <v>2.5</v>
+        <v>2.04</v>
       </c>
       <c r="T16" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="V16" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W16" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="X16" t="n">
-        <v>2.7</v>
+        <v>2.1</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.3</v>
+        <v>3.16</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>4.33</v>
+        <v>6.45</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.2</v>
+        <v>1.11</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.95</v>
+        <v>2.42</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.8</v>
+        <v>1.55</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -2542,16 +2542,16 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AH16" t="n">
         <v>1.5</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,25 +2707,25 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>AIK</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" t="n">
         <v>1</v>
       </c>
-      <c r="H18" t="n">
-        <v>2</v>
-      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" t="inlineStr">
         <is>
@@ -2733,83 +2733,83 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.08</v>
+        <v>2.2</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.5</v>
       </c>
       <c r="N18" t="n">
-        <v>2.19</v>
+        <v>2.8</v>
       </c>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P18" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['80']</t>
+          <t>['-1', '-1']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>['42', '87']</t>
+          <t>['-1']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.8</v>
+        <v>1.44</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Djurgården</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Öster</t>
+          <t>AIK</t>
         </is>
       </c>
       <c r="G19" t="n">
         <v>1</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.44</v>
+        <v>3.08</v>
       </c>
       <c r="M19" t="n">
-        <v>4.7</v>
+        <v>3.47</v>
       </c>
       <c r="N19" t="n">
-        <v>6.2</v>
+        <v>2.19</v>
       </c>
       <c r="O19" t="n">
-        <v>1.95</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>3.2</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="S19" t="n">
-        <v>3.5</v>
+        <v>2.25</v>
       </c>
       <c r="T19" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="U19" t="n">
-        <v>1.53</v>
+        <v>1.25</v>
       </c>
       <c r="V19" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.12</v>
+        <v>1.5</v>
       </c>
       <c r="X19" t="n">
-        <v>4.8</v>
+        <v>2.4</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.25</v>
+        <v>1.61</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.42</v>
+        <v>4.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.56</v>
+        <v>1.14</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>2.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['87']</t>
+          <t>['80']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42', '87']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45771.58333333334</v>
@@ -2955,22 +2955,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>GAIS</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Brommapojkarna</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,83 +2991,83 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="O20" t="n">
         <v>2.5</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O20" t="n">
+      <c r="P20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>4</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S20" t="n">
         <v>3.25</v>
       </c>
-      <c r="P20" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S20" t="n">
+      <c r="T20" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>['58']</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ20" t="n">
         <v>2.5</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>['90+2']</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>['54']</t>
-        </is>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>2.2</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45771.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al Taawon</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Al Raed</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.9</v>
+        <v>3.07</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.9</v>
+        <v>2.19</v>
       </c>
       <c r="O21" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA21" t="n">
         <v>2.4</v>
       </c>
-      <c r="P21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="X21" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>3.3</v>
-      </c>
       <c r="AB21" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['30', '40', '45+6', '49']</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>['22', '54', '74']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>1.65</v>
       </c>
       <c r="AH21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>1.83</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>2.63</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45771.625</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,22 +3223,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Al Taawon</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Al Raed</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.07</v>
+        <v>1.9</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.19</v>
+        <v>3.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>2.4</v>
       </c>
       <c r="P22" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.37</v>
       </c>
       <c r="S22" t="n">
-        <v>3.25</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>2.3</v>
+        <v>2.91</v>
       </c>
       <c r="U22" t="n">
-        <v>1.55</v>
+        <v>1.38</v>
       </c>
       <c r="V22" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W22" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="X22" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.2</v>
+        <v>1.75</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.45</v>
+        <v>1.87</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['30', '40', '45+6', '49']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['29']</t>
+          <t>['22', '54', '74']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.65</v>
+        <v>1.22</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.83</v>
+        <v>2.63</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45771.625</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Union Saint-Gilloise</t>
+          <t>Waasland-Beveren</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -3378,83 +3378,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="M23" t="n">
-        <v>3.63</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.87</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>2.4</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="R23" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.92</v>
+        <v>1.81</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AD23" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '40', '51']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['38', '73']</t>
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45771.64583333334</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3610,22 +3610,22 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Waasland-Beveren</t>
+          <t>Union Saint-Gilloise</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="M25" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="N25" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="O25" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P25" t="n">
         <v>2.15</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P25" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="U25" t="n">
-        <v>1.36</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['25', '40', '51']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['38', '73']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45771.64583333334</v>
@@ -4513,48 +4513,48 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Central Córdoba SdE</t>
+          <t>Bolívar</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Deportivo Táchira</t>
+          <t>Palmeiras</t>
         </is>
       </c>
       <c r="G32" t="n">
         <v>2</v>
       </c>
       <c r="H32" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>2</v>
       </c>
-      <c r="J32" t="n">
-        <v>1</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.34</v>
+        <v>1.94</v>
       </c>
       <c r="M32" t="n">
-        <v>4.6</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>9.4</v>
+        <v>3.93</v>
       </c>
       <c r="O32" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="P32" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>9.5</v>
+        <v>4.5</v>
       </c>
       <c r="R32" t="n">
         <v>1.44</v>
@@ -4563,59 +4563,59 @@
         <v>2.63</v>
       </c>
       <c r="T32" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U32" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V32" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W32" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>3.1</v>
+        <v>3.16</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.37</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.48</v>
+        <v>1.79</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="AB32" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>['56', '69']</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>['19', '45', '73']</t>
+        </is>
+      </c>
+      <c r="AG32" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC32" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>['4', '19']</t>
-        </is>
-      </c>
-      <c r="AF32" t="inlineStr">
-        <is>
-          <t>['37']</t>
-        </is>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.07</v>
-      </c>
       <c r="AH32" t="n">
-        <v>3</v>
+        <v>1.83</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AJ32" t="n">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45771.79166666666</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bolívar</t>
+          <t>Central Córdoba SdE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Palmeiras</t>
+          <t>Deportivo Táchira</t>
         </is>
       </c>
       <c r="G33" t="n">
         <v>2</v>
       </c>
       <c r="H33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,22 +4668,22 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.94</v>
+        <v>1.34</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>4.6</v>
       </c>
       <c r="N33" t="n">
-        <v>3.93</v>
+        <v>9.4</v>
       </c>
       <c r="O33" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="P33" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.5</v>
+        <v>9.5</v>
       </c>
       <c r="R33" t="n">
         <v>1.44</v>
@@ -4692,59 +4692,59 @@
         <v>2.63</v>
       </c>
       <c r="T33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X33" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>['4', '19']</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>['37']</t>
+        </is>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AH33" t="n">
         <v>3</v>
       </c>
-      <c r="U33" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="X33" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE33" t="inlineStr">
-        <is>
-          <t>['56', '69']</t>
-        </is>
-      </c>
-      <c r="AF33" t="inlineStr">
-        <is>
-          <t>['19', '45', '73']</t>
-        </is>
-      </c>
-      <c r="AG33" t="n">
+      <c r="AI33" t="n">
         <v>1.25</v>
       </c>
-      <c r="AH33" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AI33" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ33" t="n">
-        <v>2.75</v>
+        <v>5</v>
       </c>
       <c r="AK33" s="3" t="n">
         <v>45771.79166666666</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>USA MLS Next Pro</t>
+          <t>South America Copa Libertadores</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,109 +4771,109 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Colorado Rapids II</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Minnesota United II</t>
+          <t>Atlético Nacional</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="N34" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="O34" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="P34" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="R34" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S34" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W34" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X34" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC34" t="n">
         <v>2</v>
       </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="N34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="O34" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X34" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB34" t="n">
+      <c r="AD34" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC34" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>2.8</v>
-      </c>
       <c r="AE34" t="inlineStr">
         <is>
+          <t>['71']</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF34" t="inlineStr">
-        <is>
-          <t>['16', '45+1']</t>
-        </is>
-      </c>
       <c r="AG34" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.48</v>
+        <v>1.95</v>
       </c>
       <c r="AI34" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="AJ34" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AK34" s="3" t="n">
         <v>45771.875</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>South America Copa Libertadores</t>
+          <t>USA MLS Next Pro</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Colorado Rapids II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Atlético Nacional</t>
+          <t>Minnesota United II</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.73</v>
+        <v>2.52</v>
       </c>
       <c r="M35" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="N35" t="n">
-        <v>4.5</v>
+        <v>2.33</v>
       </c>
       <c r="O35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P35" t="n">
         <v>2.4</v>
       </c>
-      <c r="P35" t="n">
-        <v>2.1</v>
-      </c>
       <c r="Q35" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="R35" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S35" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X35" t="n">
         <v>5.5</v>
       </c>
-      <c r="R35" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S35" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T35" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X35" t="n">
-        <v>2.97</v>
-      </c>
       <c r="Y35" t="n">
-        <v>2.05</v>
+        <v>1.37</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.65</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>3.64</v>
+        <v>1.93</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.22</v>
+        <v>1.75</v>
       </c>
       <c r="AC35" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
-          <t>['71']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '45+1']</t>
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>1.95</v>
+        <v>1.48</v>
       </c>
       <c r="AI35" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AJ35" t="n">
-        <v>3</v>
+        <v>1.62</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45771.875</v>
